--- a/reports/universe_2026-08-07.xlsx
+++ b/reports/universe_2026-08-07.xlsx
@@ -19,8 +19,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 - Market Movers" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9 - Track Record" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9b - Options Paper" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 - Data Quality" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 - Run Summary" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MIDAS SELECTOR PICKS" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 - Data Quality" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 - Run Summary" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2 - Fresh Buys'!$A$1:$AB$1</definedName>
@@ -33,7 +34,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'8 - Market Movers'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'9 - Track Record'!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'9b - Options Paper'!$A$1:$T$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'10 - Data Quality'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'MIDAS SELECTOR PICKS'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'10 - Data Quality'!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -752,6 +754,64 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
+        <t>MIDAS's own ordering of tonight's eligible pool (1 = its top pick).
+(Full guide: 'READ ME FIRST' tab)</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>The stock symbol.
+(Full guide: 'READ ME FIRST' tab)</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>0-9. Traits score (0-6: trend strength, buyer margin, above the 200-day, right size) plus detector-source points. Higher = more like past winners.
+(Full guide: 'READ ME FIRST' tab)</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>The 0-6 chart-traits portion alone (comparable across eras).
+(Full guide: 'READ ME FIRST' tab)</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Which detector surfaced it (the Coiled tab is the only source with a validated positive edge).
+(Full guide: 'READ ME FIRST' tab)</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>What the CURRENT live selector scored it (readiness). The two columns disagreeing is the experiment.
+(Full guide: 'READ ME FIRST' tab)</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Tonight's reference close - the tally grades from here.
+(Full guide: 'READ ME FIRST' tab)</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>YES = tonight's real A-List also chose it. Rows where MIDAS says yes and the live system said no (or vice versa) are the head-to-head.
+(Full guide: 'READ ME FIRST' tab)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment13.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>scan</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
         <t>BLOCKER = this run's conclusions may be WRONG until fixed. WARNING = a real limitation, read before acting. INFO = context.
 (Full guide: 'READ ME FIRST' tab)</t>
       </text>
@@ -784,7 +844,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment14.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>scan</author>
@@ -1838,7 +1898,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07 15:38 local</t>
+          <t>2026-08-07 23:01 local</t>
         </is>
       </c>
     </row>
@@ -38490,6 +38550,358 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>MIDAS Score</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>Traits Part</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>Found By</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>Old Score</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>Ref Price</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>Live System Picked It?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="56" t="inlineStr">
+        <is>
+          <t>HNGE</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" s="23" t="inlineStr">
+        <is>
+          <t>orig-BUY ZONE</t>
+        </is>
+      </c>
+      <c r="F2" s="23" t="n">
+        <v>70</v>
+      </c>
+      <c r="G2" s="57" t="n">
+        <v>89.33</v>
+      </c>
+      <c r="H2" s="23" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="56" t="inlineStr">
+        <is>
+          <t>AMGN</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="23" t="inlineStr">
+        <is>
+          <t>orig-FRESH IGNITION</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="n">
+        <v>62</v>
+      </c>
+      <c r="G3" s="57" t="n">
+        <v>410.94</v>
+      </c>
+      <c r="H3" s="23" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="56" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>og-chandelier</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="n">
+        <v>60</v>
+      </c>
+      <c r="G4" s="57" t="n">
+        <v>214.42</v>
+      </c>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>HSIC</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>og-chandelier</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>51</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>NOVT</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>orig-FRESH IGNITION</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>166.37</v>
+      </c>
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>VSEC</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>orig-COILED</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>218.18</v>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>og-chandelier</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>54</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>363.86</v>
+      </c>
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>SPXL</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>og-chandelier</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>62</v>
+      </c>
+      <c r="G9" s="21" t="n">
+        <v>296.33</v>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RUNNING TALLY - MIDAS top-3 vs the live system's top-3, both graded from their own pick-night reference prices to the latest close:</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Days compared: 1   |   MIDAS average: 0.0%   |   Live system average: 0.0%   |   MIDAS ahead on 1 of 1 day(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2026-08-07: MIDAS +0.00% (HNGE, AMGN, CRWD)  vs  live +0.00% (HNGE, AMGN, SPXL)   &lt;&lt; MIDAS ahead</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   SHADOW ONLY - MIDAS ranks nothing live until the promotion decision (prereg c19b0a4)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -38642,7 +39054,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38699,7 +39111,7 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>2026-08-07 15:38 local</t>
+          <t>2026-08-07 23:01 local</t>
         </is>
       </c>
     </row>
@@ -41027,7 +41439,7 @@
         <v>64.3</v>
       </c>
       <c r="R2" s="22" t="n">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="S2" s="20" t="n">
         <v>96.5</v>
@@ -41127,7 +41539,7 @@
         <v>66.59999999999999</v>
       </c>
       <c r="R3" s="22" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="S3" s="20" t="n">
         <v>97.8</v>
@@ -41227,7 +41639,7 @@
         <v>53.8</v>
       </c>
       <c r="R4" s="22" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="S4" s="20" t="n">
         <v>92.8</v>
@@ -41431,7 +41843,7 @@
         <v>61</v>
       </c>
       <c r="R6" s="22" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="S6" s="20" t="n">
         <v>93.09999999999999</v>
@@ -41533,7 +41945,7 @@
         <v>59.4</v>
       </c>
       <c r="R7" s="22" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="S7" s="20" t="n">
         <v>92.2</v>
@@ -41717,7 +42129,7 @@
         <v>56.9</v>
       </c>
       <c r="R9" s="22" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="S9" s="20" t="n">
         <v>91.7</v>
@@ -41811,7 +42223,7 @@
         <v>59.1</v>
       </c>
       <c r="R10" s="22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="S10" s="20" t="n">
         <v>91.40000000000001</v>
@@ -42733,7 +43145,7 @@
         <v>56.2</v>
       </c>
       <c r="R20" s="22" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="S20" s="20" t="n">
         <v>85.8</v>
@@ -42911,7 +43323,7 @@
         <v>57.5</v>
       </c>
       <c r="R22" s="22" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="S22" s="20" t="n">
         <v>72</v>
@@ -43089,7 +43501,7 @@
         <v>48.1</v>
       </c>
       <c r="R24" s="22" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="S24" s="20" t="n">
         <v>87.5</v>
@@ -43189,7 +43601,7 @@
         <v>50.9</v>
       </c>
       <c r="R25" s="22" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="S25" s="20" t="n">
         <v>91.2</v>
@@ -43289,7 +43701,7 @@
         <v>49.8</v>
       </c>
       <c r="R26" s="22" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="S26" s="20" t="n">
         <v>85.40000000000001</v>
@@ -43383,7 +43795,7 @@
         <v>54.7</v>
       </c>
       <c r="R27" s="22" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="S27" s="20" t="n">
         <v>92.2</v>
@@ -43483,7 +43895,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="R28" s="29" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S28" s="27" t="n">
         <v>97.59999999999999</v>
@@ -43791,7 +44203,7 @@
         <v>74.5</v>
       </c>
       <c r="R31" s="29" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="S31" s="27" t="n">
         <v>99.7</v>
@@ -44487,7 +44899,7 @@
         <v>57</v>
       </c>
       <c r="R38" s="29" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S38" s="27" t="n">
         <v>89.3</v>
@@ -44789,7 +45201,7 @@
         <v>83.3</v>
       </c>
       <c r="R41" s="29" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="S41" s="27" t="n">
         <v>93.5</v>
@@ -44991,7 +45403,7 @@
         <v>72.8</v>
       </c>
       <c r="R43" s="29" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S43" s="27" t="n">
         <v>82.90000000000001</v>
@@ -45185,7 +45597,7 @@
         <v>63.8</v>
       </c>
       <c r="R45" s="29" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="S45" s="27" t="n">
         <v>98.90000000000001</v>
@@ -45285,7 +45697,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="R46" s="29" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="S46" s="27" t="n">
         <v>94.7</v>
@@ -45379,7 +45791,7 @@
         <v>48.7</v>
       </c>
       <c r="R47" s="29" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="S47" s="27" t="n">
         <v>46.2</v>
@@ -45473,7 +45885,7 @@
         <v>60.9</v>
       </c>
       <c r="R48" s="29" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S48" s="27" t="n">
         <v>87.59999999999999</v>
@@ -45581,7 +45993,7 @@
         <v>59.2</v>
       </c>
       <c r="R49" s="29" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="S49" s="27" t="n">
         <v>90.90000000000001</v>
@@ -45675,7 +46087,7 @@
         <v>67.40000000000001</v>
       </c>
       <c r="R50" s="29" t="n">
-        <v>17.03</v>
+        <v>17.16</v>
       </c>
       <c r="S50" s="27" t="n">
         <v>31.5</v>
@@ -45869,7 +46281,7 @@
         <v>64</v>
       </c>
       <c r="R52" s="29" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="S52" s="27" t="n">
         <v>77.90000000000001</v>
@@ -46247,7 +46659,7 @@
         <v>61.7</v>
       </c>
       <c r="R56" s="29" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="S56" s="27" t="n">
         <v>72.7</v>
@@ -46425,7 +46837,7 @@
         <v>53.7</v>
       </c>
       <c r="R58" s="29" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S58" s="27" t="n">
         <v>80</v>
@@ -46519,7 +46931,7 @@
         <v>66.2</v>
       </c>
       <c r="R59" s="29" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="S59" s="27" t="n">
         <v>87.59999999999999</v>
@@ -46721,7 +47133,7 @@
         <v>62.8</v>
       </c>
       <c r="R61" s="29" t="n">
-        <v>0.49</v>
+        <v>0.57</v>
       </c>
       <c r="S61" s="27" t="n">
         <v>98</v>
@@ -46821,7 +47233,7 @@
         <v>41.4</v>
       </c>
       <c r="R62" s="29" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="S62" s="27" t="n">
         <v>65.90000000000001</v>
@@ -46915,7 +47327,7 @@
         <v>70.59999999999999</v>
       </c>
       <c r="R63" s="29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="S63" s="27" t="n">
         <v>99.5</v>
@@ -47015,7 +47427,7 @@
         <v>69</v>
       </c>
       <c r="R64" s="29" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S64" s="27" t="n">
         <v>36.2</v>
@@ -47411,7 +47823,7 @@
         <v>56.7</v>
       </c>
       <c r="R68" s="29" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S68" s="27" t="n">
         <v>51</v>
@@ -47505,7 +47917,7 @@
         <v>55.4</v>
       </c>
       <c r="R69" s="29" t="n">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="S69" s="27" t="n">
         <v>25</v>
@@ -47599,7 +48011,7 @@
         <v>64.2</v>
       </c>
       <c r="R70" s="29" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="S70" s="27" t="n">
         <v>95.59999999999999</v>
@@ -47899,7 +48311,7 @@
         <v>42.9</v>
       </c>
       <c r="R73" s="29" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="S73" s="27" t="n">
         <v>78.5</v>
@@ -48187,7 +48599,7 @@
         <v>56.9</v>
       </c>
       <c r="R76" s="29" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="S76" s="27" t="n">
         <v>93.40000000000001</v>
@@ -48287,7 +48699,7 @@
         <v>55.4</v>
       </c>
       <c r="R77" s="29" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="S77" s="27" t="n">
         <v>59.2</v>
@@ -48489,7 +48901,7 @@
         <v>54.9</v>
       </c>
       <c r="R79" s="29" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S79" s="27" t="n">
         <v>34.8</v>
@@ -48667,7 +49079,7 @@
         <v>57.1</v>
       </c>
       <c r="R81" s="29" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="S81" s="27" t="n">
         <v>17.1</v>
@@ -48861,7 +49273,7 @@
         <v>56.2</v>
       </c>
       <c r="R83" s="29" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S83" s="27" t="n">
         <v>54.9</v>
@@ -48963,7 +49375,7 @@
         <v>56.5</v>
       </c>
       <c r="R84" s="29" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="S84" s="27" t="n">
         <v>56.2</v>
@@ -49057,7 +49469,7 @@
         <v>58.1</v>
       </c>
       <c r="R85" s="29" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S85" s="27" t="n">
         <v>73.59999999999999</v>
@@ -49151,7 +49563,7 @@
         <v>56.6</v>
       </c>
       <c r="R86" s="29" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="S86" s="27" t="n">
         <v>42.5</v>
@@ -49517,7 +49929,7 @@
         <v>47.6</v>
       </c>
       <c r="R90" s="29" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="S90" s="27" t="n">
         <v>29.5</v>
@@ -49811,7 +50223,7 @@
         <v>58.2</v>
       </c>
       <c r="R93" s="29" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="S93" s="27" t="n">
         <v>93.09999999999999</v>
@@ -50111,7 +50523,7 @@
         <v>44</v>
       </c>
       <c r="R96" s="29" t="n">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="S96" s="27" t="n">
         <v>49.8</v>
@@ -50205,7 +50617,7 @@
         <v>51</v>
       </c>
       <c r="R97" s="29" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="S97" s="27" t="n">
         <v>87.40000000000001</v>
@@ -50305,7 +50717,7 @@
         <v>52.5</v>
       </c>
       <c r="R98" s="29" t="n">
-        <v>6.27</v>
+        <v>6.37</v>
       </c>
       <c r="S98" s="27" t="n">
         <v>27.8</v>
@@ -50677,7 +51089,7 @@
         <v>52.2</v>
       </c>
       <c r="R102" s="29" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="S102" s="27" t="n">
         <v>40.6</v>
@@ -50771,7 +51183,7 @@
         <v>52.8</v>
       </c>
       <c r="R103" s="29" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S103" s="27" t="n">
         <v>35.1</v>
@@ -50873,7 +51285,7 @@
         <v>50.9</v>
       </c>
       <c r="R104" s="29" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="S104" s="27" t="n">
         <v>94.5</v>
@@ -51273,7 +51685,7 @@
         <v>54.9</v>
       </c>
       <c r="R108" s="29" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="S108" s="27" t="n">
         <v>53.7</v>
@@ -51375,7 +51787,7 @@
         <v>48.8</v>
       </c>
       <c r="R109" s="29" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S109" s="27" t="n">
         <v>80.3</v>
@@ -56285,7 +56697,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="25" t="n">
-        <v>87.8</v>
+        <v>107.8</v>
       </c>
       <c r="C2" s="26" t="inlineStr">
         <is>
@@ -56328,25 +56740,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="25" t="n">
-        <v>76.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="C3" s="26" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>BIDU</t>
         </is>
       </c>
       <c r="D3" s="26" t="inlineStr">
         <is>
-          <t>Mobileye Global, Inc. Class A</t>
+          <t>Baidu, Inc. Sponsored ADR Class A</t>
         </is>
       </c>
       <c r="E3" s="26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>1.6094</v>
+        <v>11.8664</v>
       </c>
       <c r="G3" s="26" t="inlineStr">
         <is>
@@ -56355,12 +56767,12 @@
       </c>
       <c r="H3" s="26" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-10.7064% vs the 200-day average)</t>
+          <t>regime DEEP-FAIL (-12.5269% vs the 200-day average)</t>
         </is>
       </c>
       <c r="I3" s="26" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-10.7064% vs the 200-day average) - watch only, no size; trend strength (ADX) 19.4121 below 20 - no trend to ride; -DI...</t>
+          <t>regime DEEP-FAIL (-12.5269% vs the 200-day average) - watch only, no size; -DI 22.9984 &gt;= +DI 16.7885 - sellers in cont...</t>
         </is>
       </c>
       <c r="J3" s="26" t="inlineStr"/>
@@ -56371,25 +56783,25 @@
         <v>3</v>
       </c>
       <c r="B4" s="25" t="n">
-        <v>72.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="C4" s="26" t="inlineStr">
         <is>
-          <t>BIDU</t>
+          <t>LAES</t>
         </is>
       </c>
       <c r="D4" s="26" t="inlineStr">
         <is>
-          <t>Baidu, Inc. Sponsored ADR Class A</t>
+          <t>SEALSQ Corp.</t>
         </is>
       </c>
       <c r="E4" s="26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>11.8664</v>
+        <v>18.1641</v>
       </c>
       <c r="G4" s="26" t="inlineStr">
         <is>
@@ -56398,12 +56810,12 @@
       </c>
       <c r="H4" s="26" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-12.5269% vs the 200-day average)</t>
+          <t>regime DEEP-FAIL (-31.6567% vs the 200-day average)</t>
         </is>
       </c>
       <c r="I4" s="26" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-12.5269% vs the 200-day average) - watch only, no size; -DI 22.9984 &gt;= +DI 16.7885 - sellers in cont...</t>
+          <t>regime DEEP-FAIL (-31.6567% vs the 200-day average) - watch only, no size; -DI 17.6853 &gt;= +DI 15.4569 - sellers in control</t>
         </is>
       </c>
       <c r="J4" s="26" t="inlineStr"/>
@@ -56414,16 +56826,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="25" t="n">
-        <v>68.3</v>
+        <v>76.8</v>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
-          <t>UAVS</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
-          <t>AgEagle Aerial Systems, Inc.</t>
+          <t>Mobileye Global, Inc. Class A</t>
         </is>
       </c>
       <c r="E5" s="26" t="inlineStr">
@@ -56432,7 +56844,7 @@
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>316.386</v>
+        <v>1.6094</v>
       </c>
       <c r="G5" s="26" t="inlineStr">
         <is>
@@ -56441,12 +56853,12 @@
       </c>
       <c r="H5" s="26" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-19.5341% vs the 200-day average)</t>
+          <t>regime DEEP-FAIL (-10.7064% vs the 200-day average)</t>
         </is>
       </c>
       <c r="I5" s="26" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-19.5341% vs the 200-day average) - watch only, no size; stop is 4.60x ATR (multiples of a normal day's swing) - so wide the position shr...</t>
+          <t>regime DEEP-FAIL (-10.7064% vs the 200-day average) - watch only, no size; trend strength (ADX) 19.4121 below 20 - no trend to ride; -DI...</t>
         </is>
       </c>
       <c r="J5" s="26" t="inlineStr"/>
@@ -56457,39 +56869,39 @@
         <v>5</v>
       </c>
       <c r="B6" s="25" t="n">
-        <v>65</v>
+        <v>68.3</v>
       </c>
       <c r="C6" s="26" t="inlineStr">
         <is>
-          <t>WRBY</t>
+          <t>UAVS</t>
         </is>
       </c>
       <c r="D6" s="26" t="inlineStr">
         <is>
-          <t>Warby Parker, Inc. Class A</t>
+          <t>AgEagle Aerial Systems, Inc.</t>
         </is>
       </c>
       <c r="E6" s="26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F6" s="27" t="n">
-        <v>-6.7271</v>
+        <v>316.386</v>
       </c>
       <c r="G6" s="26" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>DEEP-FAIL</t>
         </is>
       </c>
       <c r="H6" s="26" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 14.8148 below 20</t>
+          <t>regime DEEP-FAIL (-19.5341% vs the 200-day average)</t>
         </is>
       </c>
       <c r="I6" s="26" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 14.8148 below 20 - no trend to ride; -DI 20.1868 &gt;= +DI 20.0951 - sellers in control; price 26.3526 at/...</t>
+          <t>regime DEEP-FAIL (-19.5341% vs the 200-day average) - watch only, no size; stop is 4.60x ATR (multiples of a normal day's swing) - so wide the position shr...</t>
         </is>
       </c>
       <c r="J6" s="26" t="inlineStr"/>
@@ -56500,25 +56912,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="25" t="n">
-        <v>62.9</v>
+        <v>66.3</v>
       </c>
       <c r="C7" s="26" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="D7" s="26" t="inlineStr">
         <is>
-          <t>SoundHound AI, Inc Class A</t>
+          <t>NuScale Power Corporation Class A</t>
         </is>
       </c>
       <c r="E7" s="26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>279.6416</v>
+        <v>180.8613</v>
       </c>
       <c r="G7" s="26" t="inlineStr">
         <is>
@@ -56527,12 +56939,12 @@
       </c>
       <c r="H7" s="26" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-17.5885% vs the 200-day average)</t>
+          <t>regime DEEP-FAIL (-37.5702% vs the 200-day average)</t>
         </is>
       </c>
       <c r="I7" s="26" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-17.5885% vs the 200-day average) - watch only, no size; trend strength (ADX) 16.4075 below 20 - no trend to ride; sto...</t>
+          <t>regime DEEP-FAIL (-37.5702% vs the 200-day average) - watch only, no size; stop is 14.6% away - volatility cap 12%: a n...</t>
         </is>
       </c>
       <c r="J7" s="26" t="inlineStr"/>
@@ -56543,39 +56955,39 @@
         <v>7</v>
       </c>
       <c r="B8" s="25" t="n">
-        <v>62.2</v>
+        <v>65</v>
       </c>
       <c r="C8" s="26" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>WRBY</t>
         </is>
       </c>
       <c r="D8" s="26" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>Warby Parker, Inc. Class A</t>
         </is>
       </c>
       <c r="E8" s="26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>88.0314</v>
+        <v>-6.7271</v>
       </c>
       <c r="G8" s="26" t="inlineStr">
         <is>
-          <t>DEEP-FAIL</t>
+          <t>REPAIR</t>
         </is>
       </c>
       <c r="H8" s="26" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-13.0541% vs the 200-day average)</t>
+          <t>trend strength (ADX) 14.8148 below 20</t>
         </is>
       </c>
       <c r="I8" s="26" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-13.0541% vs the 200-day average) - watch only, no size; trend strength (ADX) 17.6101 below 20 - no trend to ride; sto...</t>
+          <t>trend strength (ADX) 14.8148 below 20 - no trend to ride; -DI 20.1868 &gt;= +DI 20.0951 - sellers in control; price 26.3526 at/...</t>
         </is>
       </c>
       <c r="J8" s="26" t="inlineStr"/>
@@ -56586,16 +56998,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="25" t="n">
-        <v>60.3</v>
+        <v>63.1</v>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
-          <t>LAES</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="D9" s="26" t="inlineStr">
         <is>
-          <t>SEALSQ Corp.</t>
+          <t>Rigetti Computing, Inc.</t>
         </is>
       </c>
       <c r="E9" s="26" t="inlineStr">
@@ -56604,7 +57016,7 @@
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>18.1641</v>
+        <v>157.7525</v>
       </c>
       <c r="G9" s="26" t="inlineStr">
         <is>
@@ -56613,161 +57025,169 @@
       </c>
       <c r="H9" s="26" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-31.6567% vs the 200-day average)</t>
+          <t>regime DEEP-FAIL (-18.4682% vs the 200-day average)</t>
         </is>
       </c>
       <c r="I9" s="26" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-31.6567% vs the 200-day average) - watch only, no size; -DI 17.6853 &gt;= +DI 15.4569 - sellers in control</t>
+          <t>regime DEEP-FAIL (-18.4682% vs the 200-day average) - watch only, no size; stop is 17.1% away - volatility cap 12%: a n...</t>
         </is>
       </c>
       <c r="J9" s="26" t="inlineStr"/>
       <c r="K9" s="26" t="inlineStr"/>
     </row>
     <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="34" t="n">
+      <c r="A10" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="35" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="C10" s="36" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="D10" s="36" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="E10" s="36" t="inlineStr">
+      <c r="B10" s="25" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>SOUN</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>SoundHound AI, Inc Class A</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>279.6416</v>
+      </c>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t>DEEP-FAIL</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>regime DEEP-FAIL (-17.5885% vs the 200-day average)</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr">
+        <is>
+          <t>regime DEEP-FAIL (-17.5885% vs the 200-day average) - watch only, no size; trend strength (ADX) 16.4075 below 20 - no trend to ride; sto...</t>
+        </is>
+      </c>
+      <c r="J10" s="26" t="inlineStr"/>
+      <c r="K10" s="26" t="inlineStr"/>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="25" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>ASTS</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>AST SpaceMobile, Inc. Class A</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F10" s="37" t="n">
-        <v>-35.0947</v>
-      </c>
-      <c r="G10" s="36" t="inlineStr">
+      <c r="F11" s="27" t="n">
+        <v>110.6014</v>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t>DEEP-FAIL</t>
         </is>
       </c>
-      <c r="H10" s="36" t="inlineStr">
-        <is>
-          <t>regime DEEP-FAIL (-20.1529% vs the 200-day average)</t>
-        </is>
-      </c>
-      <c r="I10" s="36" t="inlineStr">
-        <is>
-          <t>regime DEEP-FAIL (-20.1529% vs the 200-day average) - watch only, no size; -DI 22.254 &gt;= +DI 13.9454 - sellers in contr...</t>
-        </is>
-      </c>
-      <c r="J10" s="36" t="inlineStr"/>
-      <c r="K10" s="36" t="inlineStr"/>
-    </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="35" t="n">
-        <v>50</v>
-      </c>
-      <c r="C11" s="36" t="inlineStr">
-        <is>
-          <t>WMS</t>
-        </is>
-      </c>
-      <c r="D11" s="36" t="inlineStr">
-        <is>
-          <t>Advanced Drainage Systems, Inc.</t>
-        </is>
-      </c>
-      <c r="E11" s="36" t="inlineStr">
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>regime DEEP-FAIL (-14.4399% vs the 200-day average)</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>regime DEEP-FAIL (-14.4399% vs the 200-day average) - watch only, no size; stop is 13.6% away - volatility cap 12%: a n...</t>
+        </is>
+      </c>
+      <c r="J11" s="26" t="inlineStr">
+        <is>
+          <t>Earnings 2026-08-10</t>
+        </is>
+      </c>
+      <c r="K11" s="26" t="inlineStr">
+        <is>
+          <t>Reports 2026-08-10 (est EPS -0.32). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>SoFi Technologies Inc</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F11" s="37" t="n">
-        <v>36.0587</v>
-      </c>
-      <c r="G11" s="36" t="inlineStr">
-        <is>
-          <t>REPAIR</t>
-        </is>
-      </c>
-      <c r="H11" s="36" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 17.4377 below 20</t>
-        </is>
-      </c>
-      <c r="I11" s="36" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 17.4377 below 20 - no trend to ride; price 147.505 at/below its trend line (ZLSMA) 147.5783 - structure has not turned</t>
-        </is>
-      </c>
-      <c r="J11" s="36" t="inlineStr"/>
-      <c r="K11" s="36" t="inlineStr"/>
-    </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="35" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>HTZ</t>
-        </is>
-      </c>
-      <c r="D12" s="36" t="inlineStr">
-        <is>
-          <t>Hertz Global Holdings Inc</t>
-        </is>
-      </c>
-      <c r="E12" s="36" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="F12" s="37" t="n">
-        <v>257.4036</v>
-      </c>
-      <c r="G12" s="36" t="inlineStr">
+      <c r="F12" s="27" t="n">
+        <v>88.0314</v>
+      </c>
+      <c r="G12" s="26" t="inlineStr">
         <is>
           <t>DEEP-FAIL</t>
         </is>
       </c>
-      <c r="H12" s="36" t="inlineStr">
-        <is>
-          <t>regime DEEP-FAIL (-51.1236% vs the 200-day average)</t>
-        </is>
-      </c>
-      <c r="I12" s="36" t="inlineStr">
-        <is>
-          <t>regime DEEP-FAIL (-51.1236% vs the 200-day average) - watch only, no size; stop is 4.63x ATR (multiples of a normal day's swing) - so wide the position shr...</t>
-        </is>
-      </c>
-      <c r="J12" s="36" t="inlineStr"/>
-      <c r="K12" s="36" t="inlineStr"/>
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>regime DEEP-FAIL (-13.0541% vs the 200-day average)</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="inlineStr">
+        <is>
+          <t>regime DEEP-FAIL (-13.0541% vs the 200-day average) - watch only, no size; trend strength (ADX) 17.6101 below 20 - no trend to ride; sto...</t>
+        </is>
+      </c>
+      <c r="J12" s="26" t="inlineStr"/>
+      <c r="K12" s="26" t="inlineStr"/>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="34" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="35" t="n">
-        <v>46.3</v>
+        <v>58.4</v>
       </c>
       <c r="C13" s="36" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="D13" s="36" t="inlineStr">
         <is>
-          <t>NuScale Power Corporation Class A</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="E13" s="36" t="inlineStr">
@@ -56776,7 +57196,7 @@
         </is>
       </c>
       <c r="F13" s="37" t="n">
-        <v>180.8613</v>
+        <v>-35.0947</v>
       </c>
       <c r="G13" s="36" t="inlineStr">
         <is>
@@ -56785,98 +57205,98 @@
       </c>
       <c r="H13" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-37.5702% vs the 200-day average)</t>
+          <t>regime DEEP-FAIL (-20.1529% vs the 200-day average)</t>
         </is>
       </c>
       <c r="I13" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-37.5702% vs the 200-day average) - watch only, no size; stop is 14.6% away - volatility cap 12%: a n...</t>
+          <t>regime DEEP-FAIL (-20.1529% vs the 200-day average) - watch only, no size; -DI 22.254 &gt;= +DI 13.9454 - sellers in contr...</t>
         </is>
       </c>
       <c r="J13" s="36" t="inlineStr"/>
       <c r="K13" s="36" t="inlineStr"/>
     </row>
-    <row r="14" ht="45" customHeight="1">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="34" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="35" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C14" s="36" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="D14" s="36" t="inlineStr">
         <is>
-          <t>Oklo Inc. Class A</t>
+          <t>Caterpillar Inc.</t>
         </is>
       </c>
       <c r="E14" s="36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F14" s="37" t="n">
-        <v>126.831</v>
+        <v>-44.0153</v>
       </c>
       <c r="G14" s="36" t="inlineStr">
         <is>
-          <t>DEEP-FAIL</t>
+          <t>REPAIR</t>
         </is>
       </c>
       <c r="H14" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-36.2914% vs the 200-day average)</t>
+          <t>-DI 21.5551 &gt;= +DI 20.2544</t>
         </is>
       </c>
       <c r="I14" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-36.2914% vs the 200-day average) - watch only, no size; stop is 18.4% away - volatility cap 12%: a n...</t>
+          <t>-DI 21.5551 &gt;= +DI 20.2544 - sellers in control; stop is 0.82x ATR (44.0892) - inside daily noise, it gets ...</t>
         </is>
       </c>
       <c r="J14" s="36" t="inlineStr"/>
       <c r="K14" s="36" t="inlineStr"/>
     </row>
-    <row r="15" ht="45" customHeight="1">
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" s="34" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="35" t="n">
-        <v>45.3</v>
+        <v>50</v>
       </c>
       <c r="C15" s="36" t="inlineStr">
         <is>
-          <t>BBAI</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="D15" s="36" t="inlineStr">
         <is>
-          <t>BigBear.ai Holdings, Inc.</t>
+          <t>Elevance Health, Inc.</t>
         </is>
       </c>
       <c r="E15" s="36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F15" s="37" t="n">
-        <v>123.4135</v>
+        <v>36.5131</v>
       </c>
       <c r="G15" s="36" t="inlineStr">
         <is>
-          <t>DEEP-FAIL</t>
+          <t>REPAIR</t>
         </is>
       </c>
       <c r="H15" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-31.5504% vs the 200-day average)</t>
+          <t>-DI 17.3417 &gt;= +DI 15.9664</t>
         </is>
       </c>
       <c r="I15" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-31.5504% vs the 200-day average) - watch only, no size; stop is 13.4% away - volatility cap 12%: a n...</t>
+          <t>-DI 17.3417 &gt;= +DI 15.9664 - sellers in control</t>
         </is>
       </c>
       <c r="J15" s="36" t="inlineStr"/>
@@ -56887,102 +57307,102 @@
         <v>15</v>
       </c>
       <c r="B16" s="35" t="n">
-        <v>43.2</v>
+        <v>50</v>
       </c>
       <c r="C16" s="36" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D16" s="36" t="inlineStr">
         <is>
-          <t>Oracle Corporation</t>
+          <t>Alphabet Inc. Class A</t>
         </is>
       </c>
       <c r="E16" s="36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F16" s="37" t="n">
-        <v>143.4093</v>
+        <v>34.772</v>
       </c>
       <c r="G16" s="36" t="inlineStr">
         <is>
-          <t>DEEP-FAIL</t>
+          <t>REPAIR</t>
         </is>
       </c>
       <c r="H16" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-18.964% vs the 200-day average)</t>
+          <t>price 355.925 at/below its trend line (ZLSMA) 365.311</t>
         </is>
       </c>
       <c r="I16" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-18.964% vs the 200-day average) - watch only, no size</t>
+          <t>price 355.925 at/below its trend line (ZLSMA) 365.311 - structure has not turned</t>
         </is>
       </c>
       <c r="J16" s="36" t="inlineStr"/>
       <c r="K16" s="36" t="inlineStr"/>
     </row>
-    <row r="17" ht="45" customHeight="1">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="34" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="35" t="n">
-        <v>43.1</v>
+        <v>50</v>
       </c>
       <c r="C17" s="36" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="D17" s="36" t="inlineStr">
         <is>
-          <t>Rigetti Computing, Inc.</t>
+          <t>Quanta Services, Inc.</t>
         </is>
       </c>
       <c r="E17" s="36" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F17" s="37" t="n">
-        <v>157.7525</v>
+        <v>82.03270000000001</v>
       </c>
       <c r="G17" s="36" t="inlineStr">
         <is>
-          <t>DEEP-FAIL</t>
+          <t>REPAIR</t>
         </is>
       </c>
       <c r="H17" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-18.4682% vs the 200-day average)</t>
+          <t>-DI 20.0299 &gt;= +DI 16.8843</t>
         </is>
       </c>
       <c r="I17" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-18.4682% vs the 200-day average) - watch only, no size; stop is 17.1% away - volatility cap 12%: a n...</t>
+          <t>-DI 20.0299 &gt;= +DI 16.8843 - sellers in control; stop is 0.99x ATR (41.1906) - inside daily noise, it gets ...</t>
         </is>
       </c>
       <c r="J17" s="36" t="inlineStr"/>
       <c r="K17" s="36" t="inlineStr"/>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="34" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="35" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="C18" s="36" t="inlineStr">
         <is>
-          <t>LUNR</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D18" s="36" t="inlineStr">
         <is>
-          <t>Intuitive Machines, Inc. Class A</t>
+          <t>Sea Limited Sponsored ADR Class A</t>
         </is>
       </c>
       <c r="E18" s="36" t="inlineStr">
@@ -56991,101 +57411,93 @@
         </is>
       </c>
       <c r="F18" s="37" t="n">
-        <v>153.0823</v>
+        <v>111.0214</v>
       </c>
       <c r="G18" s="36" t="inlineStr">
         <is>
-          <t>DEEP-FAIL</t>
+          <t>REPAIR</t>
         </is>
       </c>
       <c r="H18" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-17.6411% vs the 200-day average)</t>
+          <t>price 113.0525 at/below its trend line (ZLSMA) 115.5271</t>
         </is>
       </c>
       <c r="I18" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-17.6411% vs the 200-day average) - watch only, no size; stop is 23.7% away - volatility cap 12%: a n...</t>
-        </is>
-      </c>
-      <c r="J18" s="36" t="inlineStr">
-        <is>
-          <t>Earnings 2026-08-13</t>
-        </is>
-      </c>
-      <c r="K18" s="36" t="inlineStr">
-        <is>
-          <t>Reports 2026-08-13 (est EPS -0.09). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
-        </is>
-      </c>
+          <t>price 113.0525 at/below its trend line (ZLSMA) 115.5271 - structure has not turned</t>
+        </is>
+      </c>
+      <c r="J18" s="36" t="inlineStr"/>
+      <c r="K18" s="36" t="inlineStr"/>
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="34" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="35" t="n">
-        <v>42.6</v>
+        <v>50</v>
       </c>
       <c r="C19" s="36" t="inlineStr">
         <is>
-          <t>ALB</t>
+          <t>WMS</t>
         </is>
       </c>
       <c r="D19" s="36" t="inlineStr">
         <is>
-          <t>Albemarle Corporation</t>
+          <t>Advanced Drainage Systems, Inc.</t>
         </is>
       </c>
       <c r="E19" s="36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F19" s="37" t="n">
-        <v>173.6496</v>
+        <v>36.0587</v>
       </c>
       <c r="G19" s="36" t="inlineStr">
         <is>
-          <t>DEEP-FAIL</t>
+          <t>REPAIR</t>
         </is>
       </c>
       <c r="H19" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-15.336% vs the 200-day average)</t>
+          <t>trend strength (ADX) 17.4377 below 20</t>
         </is>
       </c>
       <c r="I19" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-15.336% vs the 200-day average) - watch only, no size; stop is 13.9% away - volatility cap 12%: a na...</t>
+          <t>trend strength (ADX) 17.4377 below 20 - no trend to ride; price 147.505 at/below its trend line (ZLSMA) 147.5783 - structure has not turned</t>
         </is>
       </c>
       <c r="J19" s="36" t="inlineStr"/>
       <c r="K19" s="36" t="inlineStr"/>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="34" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="35" t="n">
-        <v>42.4</v>
+        <v>48.5</v>
       </c>
       <c r="C20" s="36" t="inlineStr">
         <is>
-          <t>ASTS</t>
+          <t>HTZ</t>
         </is>
       </c>
       <c r="D20" s="36" t="inlineStr">
         <is>
-          <t>AST SpaceMobile, Inc. Class A</t>
+          <t>Hertz Global Holdings Inc</t>
         </is>
       </c>
       <c r="E20" s="36" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F20" s="37" t="n">
-        <v>110.6014</v>
+        <v>257.4036</v>
       </c>
       <c r="G20" s="36" t="inlineStr">
         <is>
@@ -57094,49 +57506,41 @@
       </c>
       <c r="H20" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-14.4399% vs the 200-day average)</t>
+          <t>regime DEEP-FAIL (-51.1236% vs the 200-day average)</t>
         </is>
       </c>
       <c r="I20" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-14.4399% vs the 200-day average) - watch only, no size; stop is 13.6% away - volatility cap 12%: a n...</t>
-        </is>
-      </c>
-      <c r="J20" s="36" t="inlineStr">
-        <is>
-          <t>Earnings 2026-08-10</t>
-        </is>
-      </c>
-      <c r="K20" s="36" t="inlineStr">
-        <is>
-          <t>Reports 2026-08-10 (est EPS -0.32). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
-        </is>
-      </c>
+          <t>regime DEEP-FAIL (-51.1236% vs the 200-day average) - watch only, no size; stop is 4.63x ATR (multiples of a normal day's swing) - so wide the position shr...</t>
+        </is>
+      </c>
+      <c r="J20" s="36" t="inlineStr"/>
+      <c r="K20" s="36" t="inlineStr"/>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="34" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="35" t="n">
-        <v>42.1</v>
+        <v>46</v>
       </c>
       <c r="C21" s="36" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="D21" s="36" t="inlineStr">
         <is>
-          <t>MP Materials Corp Class A</t>
+          <t>Oklo Inc. Class A</t>
         </is>
       </c>
       <c r="E21" s="36" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F21" s="37" t="n">
-        <v>123.1622</v>
+        <v>126.831</v>
       </c>
       <c r="G21" s="36" t="inlineStr">
         <is>
@@ -57145,12 +57549,12 @@
       </c>
       <c r="H21" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-12.8281% vs the 200-day average)</t>
+          <t>regime DEEP-FAIL (-36.2914% vs the 200-day average)</t>
         </is>
       </c>
       <c r="I21" s="36" t="inlineStr">
         <is>
-          <t>regime DEEP-FAIL (-12.8281% vs the 200-day average) - watch only, no size; stop is 17.7% away - volatility cap 12%: a n...</t>
+          <t>regime DEEP-FAIL (-36.2914% vs the 200-day average) - watch only, no size; stop is 18.4% away - volatility cap 12%: a n...</t>
         </is>
       </c>
       <c r="J21" s="36" t="inlineStr"/>
@@ -57161,16 +57565,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="35" t="n">
-        <v>36</v>
+        <v>45.3</v>
       </c>
       <c r="C22" s="36" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>BBAI</t>
         </is>
       </c>
       <c r="D22" s="36" t="inlineStr">
         <is>
-          <t>Uber Technologies, Inc.</t>
+          <t>BigBear.ai Holdings, Inc.</t>
         </is>
       </c>
       <c r="E22" s="36" t="inlineStr">
@@ -57179,21 +57583,21 @@
         </is>
       </c>
       <c r="F22" s="37" t="n">
-        <v>84.0303</v>
+        <v>123.4135</v>
       </c>
       <c r="G22" s="36" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>DEEP-FAIL</t>
         </is>
       </c>
       <c r="H22" s="36" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 15.0164 below 20</t>
+          <t>regime DEEP-FAIL (-31.5504% vs the 200-day average)</t>
         </is>
       </c>
       <c r="I22" s="36" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 15.0164 below 20 - no trend to ride; stop is 13.6% away - volatility cap 12%: a name this wild shrinks ...</t>
+          <t>regime DEEP-FAIL (-31.5504% vs the 200-day average) - watch only, no size; stop is 13.4% away - volatility cap 12%: a n...</t>
         </is>
       </c>
       <c r="J22" s="36" t="inlineStr"/>
@@ -57204,59 +57608,59 @@
         <v>22</v>
       </c>
       <c r="B23" s="35" t="n">
-        <v>35.4</v>
+        <v>43.2</v>
       </c>
       <c r="C23" s="36" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="D23" s="36" t="inlineStr">
         <is>
-          <t>Carvana Co. Class A</t>
+          <t>Oracle Corporation</t>
         </is>
       </c>
       <c r="E23" s="36" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F23" s="37" t="n">
-        <v>112.9177</v>
+        <v>143.4093</v>
       </c>
       <c r="G23" s="36" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>DEEP-FAIL</t>
         </is>
       </c>
       <c r="H23" s="36" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 12.2422 below 20</t>
+          <t>regime DEEP-FAIL (-18.964% vs the 200-day average)</t>
         </is>
       </c>
       <c r="I23" s="36" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 12.2422 below 20 - no trend to ride</t>
+          <t>regime DEEP-FAIL (-18.964% vs the 200-day average) - watch only, no size</t>
         </is>
       </c>
       <c r="J23" s="36" t="inlineStr"/>
       <c r="K23" s="36" t="inlineStr"/>
     </row>
-    <row r="24" ht="45" customHeight="1">
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="34" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="35" t="n">
-        <v>35</v>
+        <v>42.9</v>
       </c>
       <c r="C24" s="36" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>LUNR</t>
         </is>
       </c>
       <c r="D24" s="36" t="inlineStr">
         <is>
-          <t>Associated Banc-Corp</t>
+          <t>Intuitive Machines, Inc. Class A</t>
         </is>
       </c>
       <c r="E24" s="36" t="inlineStr">
@@ -57265,64 +57669,72 @@
         </is>
       </c>
       <c r="F24" s="37" t="n">
-        <v>36.4658</v>
+        <v>153.0823</v>
       </c>
       <c r="G24" s="36" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEEP-FAIL</t>
         </is>
       </c>
       <c r="H24" s="36" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 19.5274 below 20</t>
+          <t>regime DEEP-FAIL (-17.6411% vs the 200-day average)</t>
         </is>
       </c>
       <c r="I24" s="36" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 19.5274 below 20 - no trend to ride; price 31.1588 at/below its trend line (ZLSMA) 31.7361 - structure has not turned; s...</t>
-        </is>
-      </c>
-      <c r="J24" s="36" t="inlineStr"/>
-      <c r="K24" s="36" t="inlineStr"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
+          <t>regime DEEP-FAIL (-17.6411% vs the 200-day average) - watch only, no size; stop is 23.7% away - volatility cap 12%: a n...</t>
+        </is>
+      </c>
+      <c r="J24" s="36" t="inlineStr">
+        <is>
+          <t>Earnings 2026-08-13</t>
+        </is>
+      </c>
+      <c r="K24" s="36" t="inlineStr">
+        <is>
+          <t>Reports 2026-08-13 (est EPS -0.09). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
       <c r="A25" s="34" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="35" t="n">
-        <v>35</v>
+        <v>42.6</v>
       </c>
       <c r="C25" s="36" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="D25" s="36" t="inlineStr">
         <is>
-          <t>Walt Disney Company</t>
+          <t>Albemarle Corporation</t>
         </is>
       </c>
       <c r="E25" s="36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F25" s="37" t="n">
-        <v>232.0311</v>
+        <v>173.6496</v>
       </c>
       <c r="G25" s="36" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>DEEP-FAIL</t>
         </is>
       </c>
       <c r="H25" s="36" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 19.614 below 20</t>
+          <t>regime DEEP-FAIL (-15.336% vs the 200-day average)</t>
         </is>
       </c>
       <c r="I25" s="36" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 19.614 below 20 - no trend to ride</t>
+          <t>regime DEEP-FAIL (-15.336% vs the 200-day average) - watch only, no size; stop is 13.9% away - volatility cap 12%: a na...</t>
         </is>
       </c>
       <c r="J25" s="36" t="inlineStr"/>
@@ -57333,68 +57745,68 @@
         <v>25</v>
       </c>
       <c r="B26" s="35" t="n">
-        <v>35</v>
+        <v>42.1</v>
       </c>
       <c r="C26" s="36" t="inlineStr">
         <is>
-          <t>MAMA</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="D26" s="36" t="inlineStr">
         <is>
-          <t>Mama's Creations, Inc.</t>
+          <t>MP Materials Corp Class A</t>
         </is>
       </c>
       <c r="E26" s="36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F26" s="37" t="n">
-        <v>16.5281</v>
+        <v>123.1622</v>
       </c>
       <c r="G26" s="36" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>DEEP-FAIL</t>
         </is>
       </c>
       <c r="H26" s="36" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 18.7613 below 20</t>
+          <t>regime DEEP-FAIL (-12.8281% vs the 200-day average)</t>
         </is>
       </c>
       <c r="I26" s="36" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 18.7613 below 20 - no trend to ride; price 18.16 at/below its trend line (ZLSMA) 18.2238 - structure has not turned; sto...</t>
+          <t>regime DEEP-FAIL (-12.8281% vs the 200-day average) - watch only, no size; stop is 17.7% away - volatility cap 12%: a n...</t>
         </is>
       </c>
       <c r="J26" s="36" t="inlineStr"/>
       <c r="K26" s="36" t="inlineStr"/>
     </row>
-    <row r="27" ht="30" customHeight="1">
+    <row r="27" ht="45" customHeight="1">
       <c r="A27" s="34" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="35" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C27" s="36" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="D27" s="36" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Uber Technologies, Inc.</t>
         </is>
       </c>
       <c r="E27" s="36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F27" s="37" t="n">
-        <v>-21.9039</v>
+        <v>84.0303</v>
       </c>
       <c r="G27" s="36" t="inlineStr">
         <is>
@@ -57403,12 +57815,12 @@
       </c>
       <c r="H27" s="36" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 15.9301 below 20</t>
+          <t>trend strength (ADX) 15.0164 below 20</t>
         </is>
       </c>
       <c r="I27" s="36" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 15.9301 below 20 - no trend to ride</t>
+          <t>trend strength (ADX) 15.0164 below 20 - no trend to ride; stop is 13.6% away - volatility cap 12%: a name this wild shrinks ...</t>
         </is>
       </c>
       <c r="J27" s="36" t="inlineStr"/>
@@ -57419,25 +57831,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="35" t="n">
-        <v>35</v>
+        <v>35.8</v>
       </c>
       <c r="C28" s="36" t="inlineStr">
         <is>
-          <t>NMAX</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="D28" s="36" t="inlineStr">
         <is>
-          <t>Newsmax Inc. Class B</t>
+          <t>CoreWeave, Inc. Class A</t>
         </is>
       </c>
       <c r="E28" s="36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F28" s="37" t="n">
-        <v>159.2376</v>
+        <v>116.8361</v>
       </c>
       <c r="G28" s="36" t="inlineStr">
         <is>
@@ -57446,22 +57858,22 @@
       </c>
       <c r="H28" s="36" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 17.7338 below 20</t>
+          <t>stop is 12.2% away</t>
         </is>
       </c>
       <c r="I28" s="36" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 17.7338 below 20 - no trend to ride; stop is 14.9% away - volatility cap 12%: a name this wild shrinks ...</t>
+          <t>stop is 12.2% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
         </is>
       </c>
       <c r="J28" s="36" t="inlineStr">
         <is>
-          <t>Earnings 2026-08-13</t>
+          <t>Earnings 2026-08-11</t>
         </is>
       </c>
       <c r="K28" s="36" t="inlineStr">
         <is>
-          <t>Reports 2026-08-13 (est EPS -0.03). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
+          <t>Reports 2026-08-11 (est EPS -1.21). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
       </c>
     </row>
@@ -57470,25 +57882,25 @@
         <v>28</v>
       </c>
       <c r="B29" s="35" t="n">
-        <v>35</v>
+        <v>35.4</v>
       </c>
       <c r="C29" s="36" t="inlineStr">
         <is>
-          <t>NPO</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="D29" s="36" t="inlineStr">
         <is>
-          <t>Enpro Inc.</t>
+          <t>Carvana Co. Class A</t>
         </is>
       </c>
       <c r="E29" s="36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F29" s="37" t="n">
-        <v>70.565</v>
+        <v>112.9177</v>
       </c>
       <c r="G29" s="36" t="inlineStr">
         <is>
@@ -57497,32 +57909,32 @@
       </c>
       <c r="H29" s="36" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 19.7983 below 20</t>
+          <t>trend strength (ADX) 12.2422 below 20</t>
         </is>
       </c>
       <c r="I29" s="36" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 19.7983 below 20 - no trend to ride</t>
+          <t>trend strength (ADX) 12.2422 below 20 - no trend to ride</t>
         </is>
       </c>
       <c r="J29" s="36" t="inlineStr"/>
       <c r="K29" s="36" t="inlineStr"/>
     </row>
-    <row r="30" ht="30" customHeight="1">
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="34" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="35" t="n">
-        <v>31.6</v>
+        <v>35</v>
       </c>
       <c r="C30" s="36" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="D30" s="36" t="inlineStr">
         <is>
-          <t>Planet Labs PBC Class A</t>
+          <t>Associated Banc-Corp</t>
         </is>
       </c>
       <c r="E30" s="36" t="inlineStr">
@@ -57531,21 +57943,21 @@
         </is>
       </c>
       <c r="F30" s="37" t="n">
-        <v>60.7415</v>
+        <v>36.4658</v>
       </c>
       <c r="G30" s="36" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H30" s="36" t="inlineStr">
         <is>
-          <t>-DI 17.5644 &gt;= +DI 14.5699</t>
+          <t>trend strength (ADX) 19.5274 below 20</t>
         </is>
       </c>
       <c r="I30" s="36" t="inlineStr">
         <is>
-          <t>-DI 17.5644 &gt;= +DI 14.5699 - sellers in control; stop is 16.1% away - volatility cap 12%: a name this wild ...</t>
+          <t>trend strength (ADX) 19.5274 below 20 - no trend to ride; price 31.1588 at/below its trend line (ZLSMA) 31.7361 - structure has not turned; s...</t>
         </is>
       </c>
       <c r="J30" s="36" t="inlineStr"/>
@@ -57556,25 +57968,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="35" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="C31" s="36" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="D31" s="36" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Limited Sponsored ADR</t>
+          <t>Walt Disney Company</t>
         </is>
       </c>
       <c r="E31" s="36" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F31" s="37" t="n">
-        <v>123.5861</v>
+        <v>232.0311</v>
       </c>
       <c r="G31" s="36" t="inlineStr">
         <is>
@@ -57583,12 +57995,12 @@
       </c>
       <c r="H31" s="36" t="inlineStr">
         <is>
-          <t>price 127.6775 at/below its trend line (ZLSMA) 135.2773</t>
+          <t>trend strength (ADX) 19.614 below 20</t>
         </is>
       </c>
       <c r="I31" s="36" t="inlineStr">
         <is>
-          <t>price 127.6775 at/below its trend line (ZLSMA) 135.2773 - structure has not turned</t>
+          <t>trend strength (ADX) 19.614 below 20 - no trend to ride</t>
         </is>
       </c>
       <c r="J31" s="36" t="inlineStr"/>
@@ -57599,125 +58011,125 @@
         <v>31</v>
       </c>
       <c r="B32" s="35" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C32" s="36" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>DRTS</t>
         </is>
       </c>
       <c r="D32" s="36" t="inlineStr">
         <is>
-          <t>Caterpillar Inc.</t>
+          <t>Alpha Tau Medical Ltd</t>
         </is>
       </c>
       <c r="E32" s="36" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F32" s="37" t="n">
-        <v>-44.0153</v>
+        <v>86.3082</v>
       </c>
       <c r="G32" s="36" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H32" s="36" t="inlineStr">
         <is>
-          <t>-DI 21.5551 &gt;= +DI 20.2544</t>
+          <t>price 13.2475 at/below its trend line (ZLSMA) 13.469</t>
         </is>
       </c>
       <c r="I32" s="36" t="inlineStr">
         <is>
-          <t>-DI 21.5551 &gt;= +DI 20.2544 - sellers in control; stop is 0.82x ATR (44.0892) - inside daily noise, it gets ...</t>
+          <t>price 13.2475 at/below its trend line (ZLSMA) 13.469 - structure has not turned</t>
         </is>
       </c>
       <c r="J32" s="36" t="inlineStr"/>
       <c r="K32" s="36" t="inlineStr"/>
     </row>
-    <row r="33" ht="15" customHeight="1">
+    <row r="33" ht="30" customHeight="1">
       <c r="A33" s="34" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="35" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C33" s="36" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="D33" s="36" t="inlineStr">
         <is>
-          <t>Elevance Health, Inc.</t>
+          <t>Edgewell Personal Care Co.</t>
         </is>
       </c>
       <c r="E33" s="36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F33" s="37" t="n">
-        <v>36.5131</v>
+        <v>22.092</v>
       </c>
       <c r="G33" s="36" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H33" s="36" t="inlineStr">
         <is>
-          <t>-DI 17.3417 &gt;= +DI 15.9664</t>
+          <t>price 28.2188 at/below its trend line (ZLSMA) 29.1099</t>
         </is>
       </c>
       <c r="I33" s="36" t="inlineStr">
         <is>
-          <t>-DI 17.3417 &gt;= +DI 15.9664 - sellers in control</t>
+          <t>price 28.2188 at/below its trend line (ZLSMA) 29.1099 - structure has not turned</t>
         </is>
       </c>
       <c r="J33" s="36" t="inlineStr"/>
       <c r="K33" s="36" t="inlineStr"/>
     </row>
-    <row r="34" ht="30" customHeight="1">
+    <row r="34" ht="15" customHeight="1">
       <c r="A34" s="34" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="35" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C34" s="36" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="D34" s="36" t="inlineStr">
         <is>
-          <t>Alphabet Inc. Class A</t>
+          <t>F5, Inc.</t>
         </is>
       </c>
       <c r="E34" s="36" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F34" s="37" t="n">
-        <v>34.772</v>
+        <v>22.9333</v>
       </c>
       <c r="G34" s="36" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H34" s="36" t="inlineStr">
         <is>
-          <t>price 355.925 at/below its trend line (ZLSMA) 365.311</t>
+          <t>-DI 16.4906 &gt;= +DI 15.3213</t>
         </is>
       </c>
       <c r="I34" s="36" t="inlineStr">
         <is>
-          <t>price 355.925 at/below its trend line (ZLSMA) 365.311 - structure has not turned</t>
+          <t>-DI 16.4906 &gt;= +DI 15.3213 - sellers in control</t>
         </is>
       </c>
       <c r="J34" s="36" t="inlineStr"/>
@@ -57728,82 +58140,82 @@
         <v>34</v>
       </c>
       <c r="B35" s="35" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C35" s="36" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="D35" s="36" t="inlineStr">
         <is>
-          <t>Microchip Technology Incorporated</t>
+          <t>Flywire Corp.</t>
         </is>
       </c>
       <c r="E35" s="36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F35" s="37" t="n">
-        <v>59.4303</v>
+        <v>64.6031</v>
       </c>
       <c r="G35" s="36" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H35" s="36" t="inlineStr">
         <is>
-          <t>-DI 24.0007 &gt;= +DI 22.335</t>
+          <t>price 18.1088 at/below its trend line (ZLSMA) 18.2483</t>
         </is>
       </c>
       <c r="I35" s="36" t="inlineStr">
         <is>
-          <t>-DI 24.0007 &gt;= +DI 22.335 - sellers in control; stop is 13.4% away - volatility cap 12%: a name this wild s...</t>
+          <t>price 18.1088 at/below its trend line (ZLSMA) 18.2483 - structure has not turned</t>
         </is>
       </c>
       <c r="J35" s="36" t="inlineStr"/>
       <c r="K35" s="36" t="inlineStr"/>
     </row>
-    <row r="36" ht="30" customHeight="1">
+    <row r="36" ht="45" customHeight="1">
       <c r="A36" s="34" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="35" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C36" s="36" t="inlineStr">
         <is>
-          <t>NVTS</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="D36" s="36" t="inlineStr">
         <is>
-          <t>Navitas Semiconductor Corporation</t>
+          <t>G-III Apparel Group, Ltd.</t>
         </is>
       </c>
       <c r="E36" s="36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F36" s="37" t="n">
-        <v>119.2922</v>
+        <v>-10.3648</v>
       </c>
       <c r="G36" s="36" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H36" s="36" t="inlineStr">
         <is>
-          <t>-DI 19.6972 &gt;= +DI 15.7319</t>
+          <t>price 35.64 at/below its trend line (ZLSMA) 35.6583</t>
         </is>
       </c>
       <c r="I36" s="36" t="inlineStr">
         <is>
-          <t>-DI 19.6972 &gt;= +DI 15.7319 - sellers in control; stop is 25.4% away - volatility cap 12%: a name this wild ...</t>
+          <t>price 35.64 at/below its trend line (ZLSMA) 35.6583 - structure has not turned; stop is 0.15x ATR (multiples of a normal day's swing) (0.9752) - inside daily no...</t>
         </is>
       </c>
       <c r="J36" s="36" t="inlineStr"/>
@@ -57814,16 +58226,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="35" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C37" s="36" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="D37" s="36" t="inlineStr">
         <is>
-          <t>Quanta Services, Inc.</t>
+          <t>Alphabet Inc. Class C</t>
         </is>
       </c>
       <c r="E37" s="36" t="inlineStr">
@@ -57832,21 +58244,21 @@
         </is>
       </c>
       <c r="F37" s="37" t="n">
-        <v>82.03270000000001</v>
+        <v>34.9942</v>
       </c>
       <c r="G37" s="36" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H37" s="36" t="inlineStr">
         <is>
-          <t>-DI 20.0299 &gt;= +DI 16.8843</t>
+          <t>price 354.78 at/below its trend line (ZLSMA) 364.2628</t>
         </is>
       </c>
       <c r="I37" s="36" t="inlineStr">
         <is>
-          <t>-DI 20.0299 &gt;= +DI 16.8843 - sellers in control; stop is 0.99x ATR (41.1906) - inside daily noise, it gets ...</t>
+          <t>price 354.78 at/below its trend line (ZLSMA) 364.2628 - structure has not turned</t>
         </is>
       </c>
       <c r="J37" s="36" t="inlineStr"/>
@@ -57857,16 +58269,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="35" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C38" s="36" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>HIMX</t>
         </is>
       </c>
       <c r="D38" s="36" t="inlineStr">
         <is>
-          <t>Sea Limited Sponsored ADR Class A</t>
+          <t>Himax Technologies, Inc. Sponsored ADR</t>
         </is>
       </c>
       <c r="E38" s="36" t="inlineStr">
@@ -57875,7 +58287,7 @@
         </is>
       </c>
       <c r="F38" s="37" t="n">
-        <v>111.0214</v>
+        <v>130.3678</v>
       </c>
       <c r="G38" s="36" t="inlineStr">
         <is>
@@ -57884,558 +58296,542 @@
       </c>
       <c r="H38" s="36" t="inlineStr">
         <is>
-          <t>price 113.0525 at/below its trend line (ZLSMA) 115.5271</t>
+          <t>stop is 17.0% away</t>
         </is>
       </c>
       <c r="I38" s="36" t="inlineStr">
         <is>
-          <t>price 113.0525 at/below its trend line (ZLSMA) 115.5271 - structure has not turned</t>
+          <t>stop is 17.0% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
         </is>
       </c>
       <c r="J38" s="36" t="inlineStr"/>
       <c r="K38" s="36" t="inlineStr"/>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="38" t="n">
+      <c r="A39" s="34" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="C39" s="40" t="inlineStr">
-        <is>
-          <t>APH</t>
-        </is>
-      </c>
-      <c r="D39" s="40" t="inlineStr">
-        <is>
-          <t>Amphenol Corporation Class A</t>
-        </is>
-      </c>
-      <c r="E39" s="40" t="inlineStr">
+      <c r="B39" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="C39" s="36" t="inlineStr">
+        <is>
+          <t>HLX</t>
+        </is>
+      </c>
+      <c r="D39" s="36" t="inlineStr">
+        <is>
+          <t>Helix Energy Solutions Group, Inc.</t>
+        </is>
+      </c>
+      <c r="E39" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F39" s="37" t="n">
+        <v>72.2013</v>
+      </c>
+      <c r="G39" s="36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H39" s="36" t="inlineStr">
+        <is>
+          <t>price 9.6941 at/below its trend line (ZLSMA) 9.9941</t>
+        </is>
+      </c>
+      <c r="I39" s="36" t="inlineStr">
+        <is>
+          <t>price 9.6941 at/below its trend line (ZLSMA) 9.9941 - structure has not turned</t>
+        </is>
+      </c>
+      <c r="J39" s="36" t="inlineStr"/>
+      <c r="K39" s="36" t="inlineStr"/>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="34" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="C40" s="36" t="inlineStr">
+        <is>
+          <t>MAMA</t>
+        </is>
+      </c>
+      <c r="D40" s="36" t="inlineStr">
+        <is>
+          <t>Mama's Creations, Inc.</t>
+        </is>
+      </c>
+      <c r="E40" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="F40" s="37" t="n">
+        <v>16.5281</v>
+      </c>
+      <c r="G40" s="36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H40" s="36" t="inlineStr">
+        <is>
+          <t>trend strength (ADX) 18.7613 below 20</t>
+        </is>
+      </c>
+      <c r="I40" s="36" t="inlineStr">
+        <is>
+          <t>trend strength (ADX) 18.7613 below 20 - no trend to ride; price 18.16 at/below its trend line (ZLSMA) 18.2238 - structure has not turned; sto...</t>
+        </is>
+      </c>
+      <c r="J40" s="36" t="inlineStr"/>
+      <c r="K40" s="36" t="inlineStr"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="34" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="C41" s="36" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="D41" s="36" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="E41" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F41" s="37" t="n">
+        <v>-21.9039</v>
+      </c>
+      <c r="G41" s="36" t="inlineStr">
+        <is>
+          <t>REPAIR</t>
+        </is>
+      </c>
+      <c r="H41" s="36" t="inlineStr">
+        <is>
+          <t>trend strength (ADX) 15.9301 below 20</t>
+        </is>
+      </c>
+      <c r="I41" s="36" t="inlineStr">
+        <is>
+          <t>trend strength (ADX) 15.9301 below 20 - no trend to ride</t>
+        </is>
+      </c>
+      <c r="J41" s="36" t="inlineStr"/>
+      <c r="K41" s="36" t="inlineStr"/>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="34" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="C42" s="36" t="inlineStr">
+        <is>
+          <t>NMAX</t>
+        </is>
+      </c>
+      <c r="D42" s="36" t="inlineStr">
+        <is>
+          <t>Newsmax Inc. Class B</t>
+        </is>
+      </c>
+      <c r="E42" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F42" s="37" t="n">
+        <v>159.2376</v>
+      </c>
+      <c r="G42" s="36" t="inlineStr">
+        <is>
+          <t>REPAIR</t>
+        </is>
+      </c>
+      <c r="H42" s="36" t="inlineStr">
+        <is>
+          <t>trend strength (ADX) 17.7338 below 20</t>
+        </is>
+      </c>
+      <c r="I42" s="36" t="inlineStr">
+        <is>
+          <t>trend strength (ADX) 17.7338 below 20 - no trend to ride; stop is 14.9% away - volatility cap 12%: a name this wild shrinks ...</t>
+        </is>
+      </c>
+      <c r="J42" s="36" t="inlineStr">
+        <is>
+          <t>Earnings 2026-08-13</t>
+        </is>
+      </c>
+      <c r="K42" s="36" t="inlineStr">
+        <is>
+          <t>Reports 2026-08-13 (est EPS -0.03). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="34" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="C43" s="36" t="inlineStr">
+        <is>
+          <t>NPO</t>
+        </is>
+      </c>
+      <c r="D43" s="36" t="inlineStr">
+        <is>
+          <t>Enpro Inc.</t>
+        </is>
+      </c>
+      <c r="E43" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F43" s="37" t="n">
+        <v>70.565</v>
+      </c>
+      <c r="G43" s="36" t="inlineStr">
+        <is>
+          <t>REPAIR</t>
+        </is>
+      </c>
+      <c r="H43" s="36" t="inlineStr">
+        <is>
+          <t>trend strength (ADX) 19.7983 below 20</t>
+        </is>
+      </c>
+      <c r="I43" s="36" t="inlineStr">
+        <is>
+          <t>trend strength (ADX) 19.7983 below 20 - no trend to ride</t>
+        </is>
+      </c>
+      <c r="J43" s="36" t="inlineStr"/>
+      <c r="K43" s="36" t="inlineStr"/>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="34" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="C44" s="36" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="D44" s="36" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc. Class A</t>
+        </is>
+      </c>
+      <c r="E44" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F44" s="37" t="n">
+        <v>211.9766</v>
+      </c>
+      <c r="G44" s="36" t="inlineStr">
+        <is>
+          <t>REPAIR</t>
+        </is>
+      </c>
+      <c r="H44" s="36" t="inlineStr">
+        <is>
+          <t>stop is 19.6% away</t>
+        </is>
+      </c>
+      <c r="I44" s="36" t="inlineStr">
+        <is>
+          <t>stop is 19.6% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
+        </is>
+      </c>
+      <c r="J44" s="36" t="inlineStr"/>
+      <c r="K44" s="36" t="inlineStr"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="34" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="C45" s="36" t="inlineStr">
+        <is>
+          <t>TRNS</t>
+        </is>
+      </c>
+      <c r="D45" s="36" t="inlineStr">
+        <is>
+          <t>Transcat, Inc.</t>
+        </is>
+      </c>
+      <c r="E45" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F45" s="37" t="n">
+        <v>178.4975</v>
+      </c>
+      <c r="G45" s="36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H45" s="36" t="inlineStr">
+        <is>
+          <t>-DI 17.4046 &gt;= +DI 15.5366</t>
+        </is>
+      </c>
+      <c r="I45" s="36" t="inlineStr">
+        <is>
+          <t>-DI 17.4046 &gt;= +DI 15.5366 - sellers in control</t>
+        </is>
+      </c>
+      <c r="J45" s="36" t="inlineStr"/>
+      <c r="K45" s="36" t="inlineStr"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="34" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="C46" s="36" t="inlineStr">
+        <is>
+          <t>VSAT</t>
+        </is>
+      </c>
+      <c r="D46" s="36" t="inlineStr">
+        <is>
+          <t>ViaSat, Inc.</t>
+        </is>
+      </c>
+      <c r="E46" s="36" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="F39" s="41" t="n">
-        <v>135.3708</v>
-      </c>
-      <c r="G39" s="40" t="inlineStr">
+      <c r="F46" s="37" t="n">
+        <v>125.0471</v>
+      </c>
+      <c r="G46" s="36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H39" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 19.9743 below 20</t>
-        </is>
-      </c>
-      <c r="I39" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 19.9743 below 20 - no trend to ride</t>
-        </is>
-      </c>
-      <c r="J39" s="40" t="inlineStr"/>
-      <c r="K39" s="40" t="inlineStr"/>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="38" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="C40" s="40" t="inlineStr">
-        <is>
-          <t>AVT</t>
-        </is>
-      </c>
-      <c r="D40" s="40" t="inlineStr">
-        <is>
-          <t>Avnet, Inc.</t>
-        </is>
-      </c>
-      <c r="E40" s="40" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="F40" s="41" t="n">
-        <v>175.7995</v>
-      </c>
-      <c r="G40" s="40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H40" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 19.0937 below 20</t>
-        </is>
-      </c>
-      <c r="I40" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 19.0937 below 20 - no trend to ride</t>
-        </is>
-      </c>
-      <c r="J40" s="40" t="inlineStr"/>
-      <c r="K40" s="40" t="inlineStr"/>
-    </row>
-    <row r="41" ht="45" customHeight="1">
-      <c r="A41" s="38" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="C41" s="40" t="inlineStr">
-        <is>
-          <t>DELL</t>
-        </is>
-      </c>
-      <c r="D41" s="40" t="inlineStr">
-        <is>
-          <t>Dell Technologies, Inc. Class C</t>
-        </is>
-      </c>
-      <c r="E41" s="40" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="F41" s="41" t="n">
-        <v>61.5426</v>
-      </c>
-      <c r="G41" s="40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H41" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 16.9855 below 20</t>
-        </is>
-      </c>
-      <c r="I41" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 16.9855 below 20 - no trend to ride; stop is 17.5% away - volatility cap 12%: a name this wild shrinks ...</t>
-        </is>
-      </c>
-      <c r="J41" s="40" t="inlineStr"/>
-      <c r="K41" s="40" t="inlineStr"/>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="38" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="C42" s="40" t="inlineStr">
-        <is>
-          <t>ETN</t>
-        </is>
-      </c>
-      <c r="D42" s="40" t="inlineStr">
-        <is>
-          <t>Eaton Corp. Plc</t>
-        </is>
-      </c>
-      <c r="E42" s="40" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="F42" s="41" t="n">
-        <v>156.8086</v>
-      </c>
-      <c r="G42" s="40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H42" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 15.6829 below 20</t>
-        </is>
-      </c>
-      <c r="I42" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 15.6829 below 20 - no trend to ride</t>
-        </is>
-      </c>
-      <c r="J42" s="40" t="inlineStr"/>
-      <c r="K42" s="40" t="inlineStr"/>
-    </row>
-    <row r="43" ht="45" customHeight="1">
-      <c r="A43" s="38" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="C43" s="40" t="inlineStr">
-        <is>
-          <t>FLR</t>
-        </is>
-      </c>
-      <c r="D43" s="40" t="inlineStr">
-        <is>
-          <t>Fluor Corporation</t>
-        </is>
-      </c>
-      <c r="E43" s="40" t="inlineStr">
+      <c r="H46" s="36" t="inlineStr">
+        <is>
+          <t>price 81.8125 at/below its trend line (ZLSMA) 82.3834</t>
+        </is>
+      </c>
+      <c r="I46" s="36" t="inlineStr">
+        <is>
+          <t>price 81.8125 at/below its trend line (ZLSMA) 82.3834 - structure has not turned</t>
+        </is>
+      </c>
+      <c r="J46" s="36" t="inlineStr"/>
+      <c r="K46" s="36" t="inlineStr"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="34" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="35" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="C47" s="36" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="D47" s="36" t="inlineStr">
+        <is>
+          <t>Planet Labs PBC Class A</t>
+        </is>
+      </c>
+      <c r="E47" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F47" s="37" t="n">
+        <v>60.7415</v>
+      </c>
+      <c r="G47" s="36" t="inlineStr">
+        <is>
+          <t>REPAIR</t>
+        </is>
+      </c>
+      <c r="H47" s="36" t="inlineStr">
+        <is>
+          <t>-DI 17.5644 &gt;= +DI 14.5699</t>
+        </is>
+      </c>
+      <c r="I47" s="36" t="inlineStr">
+        <is>
+          <t>-DI 17.5644 &gt;= +DI 14.5699 - sellers in control; stop is 16.1% away - volatility cap 12%: a name this wild ...</t>
+        </is>
+      </c>
+      <c r="J47" s="36" t="inlineStr"/>
+      <c r="K47" s="36" t="inlineStr"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="35" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="C48" s="36" t="inlineStr">
+        <is>
+          <t>BABA</t>
+        </is>
+      </c>
+      <c r="D48" s="36" t="inlineStr">
+        <is>
+          <t>Alibaba Group Holding Limited Sponsored ADR</t>
+        </is>
+      </c>
+      <c r="E48" s="36" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="F48" s="37" t="n">
+        <v>123.5861</v>
+      </c>
+      <c r="G48" s="36" t="inlineStr">
+        <is>
+          <t>REPAIR</t>
+        </is>
+      </c>
+      <c r="H48" s="36" t="inlineStr">
+        <is>
+          <t>price 127.6775 at/below its trend line (ZLSMA) 135.2773</t>
+        </is>
+      </c>
+      <c r="I48" s="36" t="inlineStr">
+        <is>
+          <t>price 127.6775 at/below its trend line (ZLSMA) 135.2773 - structure has not turned</t>
+        </is>
+      </c>
+      <c r="J48" s="36" t="inlineStr"/>
+      <c r="K48" s="36" t="inlineStr"/>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="34" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="C49" s="36" t="inlineStr">
+        <is>
+          <t>MCHP</t>
+        </is>
+      </c>
+      <c r="D49" s="36" t="inlineStr">
+        <is>
+          <t>Microchip Technology Incorporated</t>
+        </is>
+      </c>
+      <c r="E49" s="36" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F43" s="41" t="n">
-        <v>286.1782</v>
-      </c>
-      <c r="G43" s="40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H43" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 19.7549 below 20</t>
-        </is>
-      </c>
-      <c r="I43" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 19.7549 below 20 - no trend to ride; stop is 14.9% away - volatility cap 12%: a name this wild shrinks ...</t>
-        </is>
-      </c>
-      <c r="J43" s="40" t="inlineStr"/>
-      <c r="K43" s="40" t="inlineStr"/>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="38" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="C44" s="40" t="inlineStr">
-        <is>
-          <t>HUBB</t>
-        </is>
-      </c>
-      <c r="D44" s="40" t="inlineStr">
-        <is>
-          <t>Hubbell Incorporated</t>
-        </is>
-      </c>
-      <c r="E44" s="40" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="F44" s="41" t="n">
-        <v>188.1092</v>
-      </c>
-      <c r="G44" s="40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H44" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 17.9216 below 20</t>
-        </is>
-      </c>
-      <c r="I44" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 17.9216 below 20 - no trend to ride</t>
-        </is>
-      </c>
-      <c r="J44" s="40" t="inlineStr"/>
-      <c r="K44" s="40" t="inlineStr"/>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="38" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="C45" s="40" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="D45" s="40" t="inlineStr">
-        <is>
-          <t>iShares Russell 2000 ETF</t>
-        </is>
-      </c>
-      <c r="E45" s="40" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="F45" s="41" t="n">
-        <v>173.6284</v>
-      </c>
-      <c r="G45" s="40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H45" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 19.7534 below 20</t>
-        </is>
-      </c>
-      <c r="I45" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 19.7534 below 20 - no trend to ride</t>
-        </is>
-      </c>
-      <c r="J45" s="40" t="inlineStr"/>
-      <c r="K45" s="40" t="inlineStr"/>
-    </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" s="38" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="C46" s="40" t="inlineStr">
-        <is>
-          <t>MLAB</t>
-        </is>
-      </c>
-      <c r="D46" s="40" t="inlineStr">
-        <is>
-          <t>Mesa Laboratories, Inc.</t>
-        </is>
-      </c>
-      <c r="E46" s="40" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="F46" s="41" t="n">
-        <v>96.6537</v>
-      </c>
-      <c r="G46" s="40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H46" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 10.4818 below 20</t>
-        </is>
-      </c>
-      <c r="I46" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 10.4818 below 20 - no trend to ride</t>
-        </is>
-      </c>
-      <c r="J46" s="40" t="inlineStr">
-        <is>
-          <t>Earnings 2026-08-10</t>
-        </is>
-      </c>
-      <c r="K46" s="40" t="inlineStr">
-        <is>
-          <t>Reports 2026-08-10 (est EPS +2.62). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="38" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="C47" s="40" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="D47" s="40" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="E47" s="40" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="F47" s="41" t="n">
-        <v>177.2028</v>
-      </c>
-      <c r="G47" s="40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H47" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 18.3099 below 20</t>
-        </is>
-      </c>
-      <c r="I47" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 18.3099 below 20 - no trend to ride</t>
-        </is>
-      </c>
-      <c r="J47" s="40" t="inlineStr"/>
-      <c r="K47" s="40" t="inlineStr"/>
-    </row>
-    <row r="48" ht="45" customHeight="1">
-      <c r="A48" s="38" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="C48" s="40" t="inlineStr">
-        <is>
-          <t>PRAX</t>
-        </is>
-      </c>
-      <c r="D48" s="40" t="inlineStr">
-        <is>
-          <t>Praxis Precision Medicines, Inc.</t>
-        </is>
-      </c>
-      <c r="E48" s="40" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="F48" s="41" t="n">
-        <v>287.9043</v>
-      </c>
-      <c r="G48" s="40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H48" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 18.985 below 20</t>
-        </is>
-      </c>
-      <c r="I48" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 18.985 below 20 - no trend to ride; stop is 22.0% away - volatility cap 12%: a name this wild shrinks a...</t>
-        </is>
-      </c>
-      <c r="J48" s="40" t="inlineStr">
-        <is>
-          <t>Trial readout ~2027-01 (window)</t>
-        </is>
-      </c>
-      <c r="K48" s="40" t="inlineStr">
-        <is>
-          <t>Ph3 readout window ~2027-01. BINARY - can gap +/-50%. Do NOT hold a momentum long through it; awareness / defined-risk spec only, sized for total loss.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" s="38" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="C49" s="40" t="inlineStr">
-        <is>
-          <t>SLAB</t>
-        </is>
-      </c>
-      <c r="D49" s="40" t="inlineStr">
-        <is>
-          <t>Silicon Laboratories Inc.</t>
-        </is>
-      </c>
-      <c r="E49" s="40" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="F49" s="41" t="n">
-        <v>131.2927</v>
-      </c>
-      <c r="G49" s="40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H49" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 15.0402 below 20</t>
-        </is>
-      </c>
-      <c r="I49" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 15.0402 below 20 - no trend to ride</t>
-        </is>
-      </c>
-      <c r="J49" s="40" t="inlineStr">
-        <is>
-          <t>Earnings 2026-08-07</t>
-        </is>
-      </c>
-      <c r="K49" s="40" t="inlineStr">
-        <is>
-          <t>Reports 2026-08-07 (est EPS +0.69). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="45" customHeight="1">
-      <c r="A50" s="38" t="n">
+      <c r="F49" s="37" t="n">
+        <v>59.4303</v>
+      </c>
+      <c r="G49" s="36" t="inlineStr">
+        <is>
+          <t>REPAIR</t>
+        </is>
+      </c>
+      <c r="H49" s="36" t="inlineStr">
+        <is>
+          <t>-DI 24.0007 &gt;= +DI 22.335</t>
+        </is>
+      </c>
+      <c r="I49" s="36" t="inlineStr">
+        <is>
+          <t>-DI 24.0007 &gt;= +DI 22.335 - sellers in control; stop is 13.4% away - volatility cap 12%: a name this wild s...</t>
+        </is>
+      </c>
+      <c r="J49" s="36" t="inlineStr"/>
+      <c r="K49" s="36" t="inlineStr"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="34" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="C50" s="40" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="D50" s="40" t="inlineStr">
-        <is>
-          <t>Trane Technologies plc</t>
-        </is>
-      </c>
-      <c r="E50" s="40" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="F50" s="41" t="n">
-        <v>74.2243</v>
-      </c>
-      <c r="G50" s="40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H50" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 16.0255 below 20</t>
-        </is>
-      </c>
-      <c r="I50" s="40" t="inlineStr">
-        <is>
-          <t>trend strength (ADX) 16.0255 below 20 - no trend to ride; stop is 0.76x ATR (17.2799) - inside daily noise, it gets hit by n...</t>
-        </is>
-      </c>
-      <c r="J50" s="40" t="inlineStr"/>
-      <c r="K50" s="40" t="inlineStr"/>
-    </row>
-    <row r="51" ht="45" customHeight="1">
+      <c r="B50" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="C50" s="36" t="inlineStr">
+        <is>
+          <t>NVTS</t>
+        </is>
+      </c>
+      <c r="D50" s="36" t="inlineStr">
+        <is>
+          <t>Navitas Semiconductor Corporation</t>
+        </is>
+      </c>
+      <c r="E50" s="36" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F50" s="37" t="n">
+        <v>119.2922</v>
+      </c>
+      <c r="G50" s="36" t="inlineStr">
+        <is>
+          <t>REPAIR</t>
+        </is>
+      </c>
+      <c r="H50" s="36" t="inlineStr">
+        <is>
+          <t>-DI 19.6972 &gt;= +DI 15.7319</t>
+        </is>
+      </c>
+      <c r="I50" s="36" t="inlineStr">
+        <is>
+          <t>-DI 19.6972 &gt;= +DI 15.7319 - sellers in control; stop is 25.4% away - volatility cap 12%: a name this wild ...</t>
+        </is>
+      </c>
+      <c r="J50" s="36" t="inlineStr"/>
+      <c r="K50" s="36" t="inlineStr"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
       <c r="A51" s="38" t="n">
         <v>50</v>
       </c>
@@ -58444,21 +58840,21 @@
       </c>
       <c r="C51" s="40" t="inlineStr">
         <is>
-          <t>XLI</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="D51" s="40" t="inlineStr">
         <is>
-          <t>State Street Industrial Select Sector SPDR ETF</t>
+          <t>Amphenol Corporation Class A</t>
         </is>
       </c>
       <c r="E51" s="40" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F51" s="41" t="n">
-        <v>113.9258</v>
+        <v>135.3708</v>
       </c>
       <c r="G51" s="40" t="inlineStr">
         <is>
@@ -58467,12 +58863,12 @@
       </c>
       <c r="H51" s="40" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 17.1885 below 20</t>
+          <t>trend strength (ADX) 19.9743 below 20</t>
         </is>
       </c>
       <c r="I51" s="40" t="inlineStr">
         <is>
-          <t>trend strength (ADX) 17.1885 below 20 - no trend to ride; stop is 1.00x ATR (3.7609) - inside daily noise, it gets hit by no...</t>
+          <t>trend strength (ADX) 19.9743 below 20 - no trend to ride</t>
         </is>
       </c>
       <c r="J51" s="40" t="inlineStr"/>
@@ -58483,16 +58879,16 @@
         <v>51</v>
       </c>
       <c r="B52" s="39" t="n">
-        <v>15.8</v>
+        <v>20</v>
       </c>
       <c r="C52" s="40" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>ATRO</t>
         </is>
       </c>
       <c r="D52" s="40" t="inlineStr">
         <is>
-          <t>CoreWeave, Inc. Class A</t>
+          <t>Astronics Corporation</t>
         </is>
       </c>
       <c r="E52" s="40" t="inlineStr">
@@ -58501,21 +58897,21 @@
         </is>
       </c>
       <c r="F52" s="41" t="n">
-        <v>116.8361</v>
+        <v>144.6866</v>
       </c>
       <c r="G52" s="40" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H52" s="40" t="inlineStr">
         <is>
-          <t>stop is 12.2% away</t>
+          <t>stop is 12.5% away</t>
         </is>
       </c>
       <c r="I52" s="40" t="inlineStr">
         <is>
-          <t>stop is 12.2% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
+          <t>stop is 12.5% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
         </is>
       </c>
       <c r="J52" s="40" t="inlineStr">
@@ -58525,34 +58921,34 @@
       </c>
       <c r="K52" s="40" t="inlineStr">
         <is>
-          <t>Reports 2026-08-11 (est EPS -1.21). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="45" customHeight="1">
+          <t>Reports 2026-08-11 (est EPS +0.59). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
       <c r="A53" s="38" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C53" s="40" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AVT</t>
         </is>
       </c>
       <c r="D53" s="40" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Avnet, Inc.</t>
         </is>
       </c>
       <c r="E53" s="40" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F53" s="41" t="n">
-        <v>106.4091</v>
+        <v>175.7995</v>
       </c>
       <c r="G53" s="40" t="inlineStr">
         <is>
@@ -58561,32 +58957,32 @@
       </c>
       <c r="H53" s="40" t="inlineStr">
         <is>
-          <t>price 274.6025 at/below its trend line (ZLSMA) 276.6194</t>
+          <t>trend strength (ADX) 19.0937 below 20</t>
         </is>
       </c>
       <c r="I53" s="40" t="inlineStr">
         <is>
-          <t>price 274.6025 at/below its trend line (ZLSMA) 276.6194 - structure has not turned; stop is 0.85x ATR (multiples of a normal day's swing) (13.1266) - inside dai...</t>
+          <t>trend strength (ADX) 19.0937 below 20 - no trend to ride</t>
         </is>
       </c>
       <c r="J53" s="40" t="inlineStr"/>
       <c r="K53" s="40" t="inlineStr"/>
     </row>
-    <row r="54" ht="30" customHeight="1">
+    <row r="54" ht="45" customHeight="1">
       <c r="A54" s="38" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C54" s="40" t="inlineStr">
         <is>
-          <t>CENX</t>
+          <t>BELFB</t>
         </is>
       </c>
       <c r="D54" s="40" t="inlineStr">
         <is>
-          <t>Century Aluminum Company</t>
+          <t>Bel Fuse Inc. Class B</t>
         </is>
       </c>
       <c r="E54" s="40" t="inlineStr">
@@ -58595,41 +58991,41 @@
         </is>
       </c>
       <c r="F54" s="41" t="n">
-        <v>225.0662</v>
+        <v>113.7309</v>
       </c>
       <c r="G54" s="40" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H54" s="40" t="inlineStr">
         <is>
-          <t>stop is 15.3% away</t>
+          <t>stop is 0.83x ATR (multiples of a normal day's swing) (22.1602)</t>
         </is>
       </c>
       <c r="I54" s="40" t="inlineStr">
         <is>
-          <t>stop is 15.3% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
+          <t>stop is 0.83x ATR (22.1602) - inside daily noise, it gets hit by nothing happening (floor 1.0x)</t>
         </is>
       </c>
       <c r="J54" s="40" t="inlineStr"/>
       <c r="K54" s="40" t="inlineStr"/>
     </row>
-    <row r="55" ht="30" customHeight="1">
+    <row r="55" ht="45" customHeight="1">
       <c r="A55" s="38" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C55" s="40" t="inlineStr">
         <is>
-          <t>DRTS</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="D55" s="40" t="inlineStr">
         <is>
-          <t>Alpha Tau Medical Ltd</t>
+          <t>Dell Technologies, Inc. Class C</t>
         </is>
       </c>
       <c r="E55" s="40" t="inlineStr">
@@ -58638,7 +59034,7 @@
         </is>
       </c>
       <c r="F55" s="41" t="n">
-        <v>86.3082</v>
+        <v>61.5426</v>
       </c>
       <c r="G55" s="40" t="inlineStr">
         <is>
@@ -58647,41 +59043,41 @@
       </c>
       <c r="H55" s="40" t="inlineStr">
         <is>
-          <t>price 13.2475 at/below its trend line (ZLSMA) 13.469</t>
+          <t>trend strength (ADX) 16.9855 below 20</t>
         </is>
       </c>
       <c r="I55" s="40" t="inlineStr">
         <is>
-          <t>price 13.2475 at/below its trend line (ZLSMA) 13.469 - structure has not turned</t>
+          <t>trend strength (ADX) 16.9855 below 20 - no trend to ride; stop is 17.5% away - volatility cap 12%: a name this wild shrinks ...</t>
         </is>
       </c>
       <c r="J55" s="40" t="inlineStr"/>
       <c r="K55" s="40" t="inlineStr"/>
     </row>
-    <row r="56" ht="30" customHeight="1">
+    <row r="56" ht="45" customHeight="1">
       <c r="A56" s="38" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C56" s="40" t="inlineStr">
         <is>
-          <t>EPC</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="D56" s="40" t="inlineStr">
         <is>
-          <t>Edgewell Personal Care Co.</t>
+          <t>Wall Street Cash</t>
         </is>
       </c>
       <c r="E56" s="40" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="F56" s="41" t="n">
-        <v>22.092</v>
+        <v>142.3284</v>
       </c>
       <c r="G56" s="40" t="inlineStr">
         <is>
@@ -58690,12 +59086,12 @@
       </c>
       <c r="H56" s="40" t="inlineStr">
         <is>
-          <t>price 28.2188 at/below its trend line (ZLSMA) 29.1099</t>
+          <t>stop is 0.98x ATR (multiples of a normal day's swing) (816.7811)</t>
         </is>
       </c>
       <c r="I56" s="40" t="inlineStr">
         <is>
-          <t>price 28.2188 at/below its trend line (ZLSMA) 29.1099 - structure has not turned</t>
+          <t>stop is 0.98x ATR (816.7811) - inside daily noise, it gets hit by nothing happening (floor 1.0x)</t>
         </is>
       </c>
       <c r="J56" s="40" t="inlineStr"/>
@@ -58706,25 +59102,25 @@
         <v>56</v>
       </c>
       <c r="B57" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C57" s="40" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="D57" s="40" t="inlineStr">
         <is>
-          <t>Energy Transfer LP</t>
+          <t>Eaton Corp. Plc</t>
         </is>
       </c>
       <c r="E57" s="40" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F57" s="41" t="n">
-        <v>-26.4282</v>
+        <v>156.8086</v>
       </c>
       <c r="G57" s="40" t="inlineStr">
         <is>
@@ -58733,41 +59129,41 @@
       </c>
       <c r="H57" s="40" t="inlineStr">
         <is>
-          <t>price 20.2188 at/below its trend line (ZLSMA) 21.2118</t>
+          <t>trend strength (ADX) 15.6829 below 20</t>
         </is>
       </c>
       <c r="I57" s="40" t="inlineStr">
         <is>
-          <t>price 20.2188 at/below its trend line (ZLSMA) 21.2118 - structure has not turned</t>
+          <t>trend strength (ADX) 15.6829 below 20 - no trend to ride</t>
         </is>
       </c>
       <c r="J57" s="40" t="inlineStr"/>
       <c r="K57" s="40" t="inlineStr"/>
     </row>
-    <row r="58" ht="15" customHeight="1">
+    <row r="58" ht="45" customHeight="1">
       <c r="A58" s="38" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C58" s="40" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>FLR</t>
         </is>
       </c>
       <c r="D58" s="40" t="inlineStr">
         <is>
-          <t>F5, Inc.</t>
+          <t>Fluor Corporation</t>
         </is>
       </c>
       <c r="E58" s="40" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F58" s="41" t="n">
-        <v>22.9333</v>
+        <v>286.1782</v>
       </c>
       <c r="G58" s="40" t="inlineStr">
         <is>
@@ -58776,41 +59172,41 @@
       </c>
       <c r="H58" s="40" t="inlineStr">
         <is>
-          <t>-DI 16.4906 &gt;= +DI 15.3213</t>
+          <t>trend strength (ADX) 19.7549 below 20</t>
         </is>
       </c>
       <c r="I58" s="40" t="inlineStr">
         <is>
-          <t>-DI 16.4906 &gt;= +DI 15.3213 - sellers in control</t>
+          <t>trend strength (ADX) 19.7549 below 20 - no trend to ride; stop is 14.9% away - volatility cap 12%: a name this wild shrinks ...</t>
         </is>
       </c>
       <c r="J58" s="40" t="inlineStr"/>
       <c r="K58" s="40" t="inlineStr"/>
     </row>
-    <row r="59" ht="30" customHeight="1">
+    <row r="59" ht="45" customHeight="1">
       <c r="A59" s="38" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C59" s="40" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>HNST</t>
         </is>
       </c>
       <c r="D59" s="40" t="inlineStr">
         <is>
-          <t>Flywire Corp.</t>
+          <t>Honest Company, Inc.</t>
         </is>
       </c>
       <c r="E59" s="40" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F59" s="41" t="n">
-        <v>64.6031</v>
+        <v>356.2927</v>
       </c>
       <c r="G59" s="40" t="inlineStr">
         <is>
@@ -58819,84 +59215,84 @@
       </c>
       <c r="H59" s="40" t="inlineStr">
         <is>
-          <t>price 18.1088 at/below its trend line (ZLSMA) 18.2483</t>
+          <t>stop is 6.64x ATR (multiples of a normal day's swing)</t>
         </is>
       </c>
       <c r="I59" s="40" t="inlineStr">
         <is>
-          <t>price 18.1088 at/below its trend line (ZLSMA) 18.2483 - structure has not turned</t>
+          <t>stop is 6.64x ATR (multiples of a normal day's swing) - so wide the position shrinks to a token (ceiling 4.0x); stop is 36.3% away - volatility...</t>
         </is>
       </c>
       <c r="J59" s="40" t="inlineStr"/>
       <c r="K59" s="40" t="inlineStr"/>
     </row>
-    <row r="60" ht="45" customHeight="1">
+    <row r="60" ht="30" customHeight="1">
       <c r="A60" s="38" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C60" s="40" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>HUBB</t>
         </is>
       </c>
       <c r="D60" s="40" t="inlineStr">
         <is>
-          <t>First Solar, Inc.</t>
+          <t>Hubbell Incorporated</t>
         </is>
       </c>
       <c r="E60" s="40" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F60" s="41" t="n">
-        <v>200.8589</v>
+        <v>188.1092</v>
       </c>
       <c r="G60" s="40" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H60" s="40" t="inlineStr">
         <is>
-          <t>stop is 4.12x ATR (multiples of a normal day's swing)</t>
+          <t>trend strength (ADX) 17.9216 below 20</t>
         </is>
       </c>
       <c r="I60" s="40" t="inlineStr">
         <is>
-          <t>stop is 4.12x ATR (multiples of a normal day's swing) - so wide the position shrinks to a token (ceiling 4.0x); stop is 22.1% away - volatility...</t>
+          <t>trend strength (ADX) 17.9216 below 20 - no trend to ride</t>
         </is>
       </c>
       <c r="J60" s="40" t="inlineStr"/>
       <c r="K60" s="40" t="inlineStr"/>
     </row>
-    <row r="61" ht="45" customHeight="1">
+    <row r="61" ht="30" customHeight="1">
       <c r="A61" s="38" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C61" s="40" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="D61" s="40" t="inlineStr">
         <is>
-          <t>G-III Apparel Group, Ltd.</t>
+          <t>iShares Russell 2000 ETF</t>
         </is>
       </c>
       <c r="E61" s="40" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F61" s="41" t="n">
-        <v>-10.3648</v>
+        <v>173.6284</v>
       </c>
       <c r="G61" s="40" t="inlineStr">
         <is>
@@ -58905,41 +59301,41 @@
       </c>
       <c r="H61" s="40" t="inlineStr">
         <is>
-          <t>price 35.64 at/below its trend line (ZLSMA) 35.6583</t>
+          <t>trend strength (ADX) 19.7534 below 20</t>
         </is>
       </c>
       <c r="I61" s="40" t="inlineStr">
         <is>
-          <t>price 35.64 at/below its trend line (ZLSMA) 35.6583 - structure has not turned; stop is 0.15x ATR (multiples of a normal day's swing) (0.9752) - inside daily no...</t>
+          <t>trend strength (ADX) 19.7534 below 20 - no trend to ride</t>
         </is>
       </c>
       <c r="J61" s="40" t="inlineStr"/>
       <c r="K61" s="40" t="inlineStr"/>
     </row>
-    <row r="62" ht="30" customHeight="1">
+    <row r="62" ht="60" customHeight="1">
       <c r="A62" s="38" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C62" s="40" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>MLAB</t>
         </is>
       </c>
       <c r="D62" s="40" t="inlineStr">
         <is>
-          <t>Alphabet Inc. Class C</t>
+          <t>Mesa Laboratories, Inc.</t>
         </is>
       </c>
       <c r="E62" s="40" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F62" s="41" t="n">
-        <v>34.9942</v>
+        <v>96.6537</v>
       </c>
       <c r="G62" s="40" t="inlineStr">
         <is>
@@ -58948,55 +59344,63 @@
       </c>
       <c r="H62" s="40" t="inlineStr">
         <is>
-          <t>price 354.78 at/below its trend line (ZLSMA) 364.2628</t>
+          <t>trend strength (ADX) 10.4818 below 20</t>
         </is>
       </c>
       <c r="I62" s="40" t="inlineStr">
         <is>
-          <t>price 354.78 at/below its trend line (ZLSMA) 364.2628 - structure has not turned</t>
-        </is>
-      </c>
-      <c r="J62" s="40" t="inlineStr"/>
-      <c r="K62" s="40" t="inlineStr"/>
-    </row>
-    <row r="63" ht="30" customHeight="1">
+          <t>trend strength (ADX) 10.4818 below 20 - no trend to ride</t>
+        </is>
+      </c>
+      <c r="J62" s="40" t="inlineStr">
+        <is>
+          <t>Earnings 2026-08-10</t>
+        </is>
+      </c>
+      <c r="K62" s="40" t="inlineStr">
+        <is>
+          <t>Reports 2026-08-10 (est EPS +2.62). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="45" customHeight="1">
       <c r="A63" s="38" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C63" s="40" t="inlineStr">
         <is>
-          <t>HIMX</t>
+          <t>NTRA</t>
         </is>
       </c>
       <c r="D63" s="40" t="inlineStr">
         <is>
-          <t>Himax Technologies, Inc. Sponsored ADR</t>
+          <t>Natera, Inc.</t>
         </is>
       </c>
       <c r="E63" s="40" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F63" s="41" t="n">
-        <v>130.3678</v>
+        <v>425.2543</v>
       </c>
       <c r="G63" s="40" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H63" s="40" t="inlineStr">
         <is>
-          <t>stop is 17.0% away</t>
+          <t>stop is 5.47x ATR (multiples of a normal day's swing)</t>
         </is>
       </c>
       <c r="I63" s="40" t="inlineStr">
         <is>
-          <t>stop is 17.0% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
+          <t>stop is 5.47x ATR (multiples of a normal day's swing) - so wide the position shrinks to a token (ceiling 4.0x); stop is 20.5% away - volatility...</t>
         </is>
       </c>
       <c r="J63" s="40" t="inlineStr"/>
@@ -59007,25 +59411,25 @@
         <v>63</v>
       </c>
       <c r="B64" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C64" s="40" t="inlineStr">
         <is>
-          <t>HLX</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D64" s="40" t="inlineStr">
         <is>
-          <t>Helix Energy Solutions Group, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="E64" s="40" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F64" s="41" t="n">
-        <v>72.2013</v>
+        <v>177.2028</v>
       </c>
       <c r="G64" s="40" t="inlineStr">
         <is>
@@ -59034,84 +59438,92 @@
       </c>
       <c r="H64" s="40" t="inlineStr">
         <is>
-          <t>price 9.6941 at/below its trend line (ZLSMA) 9.9941</t>
+          <t>trend strength (ADX) 18.3099 below 20</t>
         </is>
       </c>
       <c r="I64" s="40" t="inlineStr">
         <is>
-          <t>price 9.6941 at/below its trend line (ZLSMA) 9.9941 - structure has not turned</t>
+          <t>trend strength (ADX) 18.3099 below 20 - no trend to ride</t>
         </is>
       </c>
       <c r="J64" s="40" t="inlineStr"/>
       <c r="K64" s="40" t="inlineStr"/>
     </row>
-    <row r="65" ht="30" customHeight="1">
+    <row r="65" ht="45" customHeight="1">
       <c r="A65" s="38" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C65" s="40" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>PCVX</t>
         </is>
       </c>
       <c r="D65" s="40" t="inlineStr">
         <is>
-          <t>Innodata Inc.</t>
+          <t>Vaxcyte, Inc.</t>
         </is>
       </c>
       <c r="E65" s="40" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F65" s="41" t="n">
-        <v>120.0567</v>
+        <v>193.9287</v>
       </c>
       <c r="G65" s="40" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H65" s="40" t="inlineStr">
         <is>
-          <t>stop is 16.9% away</t>
+          <t>stop is 12.3% away</t>
         </is>
       </c>
       <c r="I65" s="40" t="inlineStr">
         <is>
-          <t>stop is 16.9% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
-        </is>
-      </c>
-      <c r="J65" s="40" t="inlineStr"/>
-      <c r="K65" s="40" t="inlineStr"/>
+          <t>stop is 12.3% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
+        </is>
+      </c>
+      <c r="J65" s="40" t="inlineStr">
+        <is>
+          <t>Trial readout ~2027-03 (window)</t>
+        </is>
+      </c>
+      <c r="K65" s="40" t="inlineStr">
+        <is>
+          <t>Ph3 readout window ~2027-03. BINARY - can gap +/-50%. Do NOT hold a momentum long through it; awareness / defined-risk spec only, sized for total loss.</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="45" customHeight="1">
       <c r="A66" s="38" t="n">
         <v>65</v>
       </c>
       <c r="B66" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C66" s="40" t="inlineStr">
         <is>
-          <t>MATX</t>
+          <t>PRAX</t>
         </is>
       </c>
       <c r="D66" s="40" t="inlineStr">
         <is>
-          <t>Matson, Inc.</t>
+          <t>Praxis Precision Medicines, Inc.</t>
         </is>
       </c>
       <c r="E66" s="40" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F66" s="41" t="n">
-        <v>-47.962</v>
+        <v>287.9043</v>
       </c>
       <c r="G66" s="40" t="inlineStr">
         <is>
@@ -59120,32 +59532,40 @@
       </c>
       <c r="H66" s="40" t="inlineStr">
         <is>
-          <t>price 206.475 at/below its trend line (ZLSMA) 211.6074</t>
+          <t>trend strength (ADX) 18.985 below 20</t>
         </is>
       </c>
       <c r="I66" s="40" t="inlineStr">
         <is>
-          <t>price 206.475 at/below its trend line (ZLSMA) 211.6074 - structure has not turned; stop is 0.80x ATR (multiples of a normal day's swing) (9.848) - inside daily ...</t>
-        </is>
-      </c>
-      <c r="J66" s="40" t="inlineStr"/>
-      <c r="K66" s="40" t="inlineStr"/>
-    </row>
-    <row r="67" ht="30" customHeight="1">
+          <t>trend strength (ADX) 18.985 below 20 - no trend to ride; stop is 22.0% away - volatility cap 12%: a name this wild shrinks a...</t>
+        </is>
+      </c>
+      <c r="J66" s="40" t="inlineStr">
+        <is>
+          <t>Trial readout ~2027-01 (window)</t>
+        </is>
+      </c>
+      <c r="K66" s="40" t="inlineStr">
+        <is>
+          <t>Ph3 readout window ~2027-01. BINARY - can gap +/-50%. Do NOT hold a momentum long through it; awareness / defined-risk spec only, sized for total loss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="45" customHeight="1">
       <c r="A67" s="38" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C67" s="40" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>PRLB</t>
         </is>
       </c>
       <c r="D67" s="40" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc. Class A</t>
+          <t>Proto Labs, Inc.</t>
         </is>
       </c>
       <c r="E67" s="40" t="inlineStr">
@@ -59154,101 +59574,101 @@
         </is>
       </c>
       <c r="F67" s="41" t="n">
-        <v>211.9766</v>
+        <v>172.2101</v>
       </c>
       <c r="G67" s="40" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H67" s="40" t="inlineStr">
         <is>
-          <t>stop is 19.6% away</t>
+          <t>stop is 0.85x ATR (multiples of a normal day's swing) (5.17)</t>
         </is>
       </c>
       <c r="I67" s="40" t="inlineStr">
         <is>
-          <t>stop is 19.6% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
+          <t>stop is 0.85x ATR (5.17) - inside daily noise, it gets hit by nothing happening (floor 1.0x)</t>
         </is>
       </c>
       <c r="J67" s="40" t="inlineStr"/>
       <c r="K67" s="40" t="inlineStr"/>
     </row>
-    <row r="68" ht="60" customHeight="1">
+    <row r="68" ht="45" customHeight="1">
       <c r="A68" s="38" t="n">
         <v>67</v>
       </c>
       <c r="B68" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C68" s="40" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>RYTM</t>
         </is>
       </c>
       <c r="D68" s="40" t="inlineStr">
         <is>
-          <t>Rocket Lab Corporation</t>
+          <t>Rhythm Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="E68" s="40" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F68" s="41" t="n">
-        <v>140.8987</v>
+        <v>214.4017</v>
       </c>
       <c r="G68" s="40" t="inlineStr">
         <is>
-          <t>REPAIR</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H68" s="40" t="inlineStr">
         <is>
-          <t>stop is 23.7% away</t>
+          <t>stop is 13.5% away</t>
         </is>
       </c>
       <c r="I68" s="40" t="inlineStr">
         <is>
-          <t>stop is 23.7% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
+          <t>stop is 13.5% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
         </is>
       </c>
       <c r="J68" s="40" t="inlineStr">
         <is>
-          <t>Earnings 2026-08-10</t>
+          <t>Trial readout ~2027-03-13 (window)</t>
         </is>
       </c>
       <c r="K68" s="40" t="inlineStr">
         <is>
-          <t>Reports 2026-08-10 (est EPS -0.06). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="30" customHeight="1">
+          <t>Ph3 readout window ~2027-03-13. BINARY - can gap +/-50%. Do NOT hold a momentum long through it; awareness / defined-risk spec only, sized for total loss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="60" customHeight="1">
       <c r="A69" s="38" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C69" s="40" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>SLAB</t>
         </is>
       </c>
       <c r="D69" s="40" t="inlineStr">
         <is>
-          <t>SentinelOne, Inc. Class A</t>
+          <t>Silicon Laboratories Inc.</t>
         </is>
       </c>
       <c r="E69" s="40" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F69" s="41" t="n">
-        <v>157.2875</v>
+        <v>131.2927</v>
       </c>
       <c r="G69" s="40" t="inlineStr">
         <is>
@@ -59257,41 +59677,49 @@
       </c>
       <c r="H69" s="40" t="inlineStr">
         <is>
-          <t>price 21.2946 at/below its trend line (ZLSMA) 21.6135</t>
+          <t>trend strength (ADX) 15.0402 below 20</t>
         </is>
       </c>
       <c r="I69" s="40" t="inlineStr">
         <is>
-          <t>price 21.2946 at/below its trend line (ZLSMA) 21.6135 - structure has not turned</t>
-        </is>
-      </c>
-      <c r="J69" s="40" t="inlineStr"/>
-      <c r="K69" s="40" t="inlineStr"/>
-    </row>
-    <row r="70" ht="15" customHeight="1">
+          <t>trend strength (ADX) 15.0402 below 20 - no trend to ride</t>
+        </is>
+      </c>
+      <c r="J69" s="40" t="inlineStr">
+        <is>
+          <t>Earnings 2026-08-07</t>
+        </is>
+      </c>
+      <c r="K69" s="40" t="inlineStr">
+        <is>
+          <t>Reports 2026-08-07 (est EPS +0.69). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
       <c r="A70" s="38" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C70" s="40" t="inlineStr">
         <is>
-          <t>TRNS</t>
+          <t>SRRK</t>
         </is>
       </c>
       <c r="D70" s="40" t="inlineStr">
         <is>
-          <t>Transcat, Inc.</t>
+          <t>Scholar Rock Holding Corp.</t>
         </is>
       </c>
       <c r="E70" s="40" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F70" s="41" t="n">
-        <v>178.4975</v>
+        <v>73.3227</v>
       </c>
       <c r="G70" s="40" t="inlineStr">
         <is>
@@ -59300,41 +59728,41 @@
       </c>
       <c r="H70" s="40" t="inlineStr">
         <is>
-          <t>-DI 17.4046 &gt;= +DI 15.5366</t>
+          <t>stop is 16.2% away</t>
         </is>
       </c>
       <c r="I70" s="40" t="inlineStr">
         <is>
-          <t>-DI 17.4046 &gt;= +DI 15.5366 - sellers in control</t>
+          <t>stop is 16.2% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
         </is>
       </c>
       <c r="J70" s="40" t="inlineStr"/>
       <c r="K70" s="40" t="inlineStr"/>
     </row>
-    <row r="71" ht="30" customHeight="1">
+    <row r="71" ht="45" customHeight="1">
       <c r="A71" s="38" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C71" s="40" t="inlineStr">
         <is>
-          <t>VSAT</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="D71" s="40" t="inlineStr">
         <is>
-          <t>ViaSat, Inc.</t>
+          <t>Trane Technologies plc</t>
         </is>
       </c>
       <c r="E71" s="40" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F71" s="41" t="n">
-        <v>125.0471</v>
+        <v>74.2243</v>
       </c>
       <c r="G71" s="40" t="inlineStr">
         <is>
@@ -59343,32 +59771,32 @@
       </c>
       <c r="H71" s="40" t="inlineStr">
         <is>
-          <t>price 81.8125 at/below its trend line (ZLSMA) 82.3834</t>
+          <t>trend strength (ADX) 16.0255 below 20</t>
         </is>
       </c>
       <c r="I71" s="40" t="inlineStr">
         <is>
-          <t>price 81.8125 at/below its trend line (ZLSMA) 82.3834 - structure has not turned</t>
+          <t>trend strength (ADX) 16.0255 below 20 - no trend to ride; stop is 0.76x ATR (17.2799) - inside daily noise, it gets hit by n...</t>
         </is>
       </c>
       <c r="J71" s="40" t="inlineStr"/>
       <c r="K71" s="40" t="inlineStr"/>
     </row>
-    <row r="72" ht="60" customHeight="1">
+    <row r="72" ht="30" customHeight="1">
       <c r="A72" s="38" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="39" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C72" s="40" t="inlineStr">
         <is>
-          <t>ATRO</t>
+          <t>VSEC</t>
         </is>
       </c>
       <c r="D72" s="40" t="inlineStr">
         <is>
-          <t>Astronics Corporation</t>
+          <t>VSE Corporation</t>
         </is>
       </c>
       <c r="E72" s="40" t="inlineStr">
@@ -59377,7 +59805,7 @@
         </is>
       </c>
       <c r="F72" s="41" t="n">
-        <v>144.6866</v>
+        <v>169.8721</v>
       </c>
       <c r="G72" s="40" t="inlineStr">
         <is>
@@ -59386,49 +59814,41 @@
       </c>
       <c r="H72" s="40" t="inlineStr">
         <is>
-          <t>stop is 12.5% away</t>
+          <t>stop is 12.4% away</t>
         </is>
       </c>
       <c r="I72" s="40" t="inlineStr">
         <is>
-          <t>stop is 12.5% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
-        </is>
-      </c>
-      <c r="J72" s="40" t="inlineStr">
-        <is>
-          <t>Earnings 2026-08-11</t>
-        </is>
-      </c>
-      <c r="K72" s="40" t="inlineStr">
-        <is>
-          <t>Reports 2026-08-11 (est EPS +0.59). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="45" customHeight="1">
+          <t>stop is 12.4% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
+        </is>
+      </c>
+      <c r="J72" s="40" t="inlineStr"/>
+      <c r="K72" s="40" t="inlineStr"/>
+    </row>
+    <row r="73" ht="30" customHeight="1">
       <c r="A73" s="38" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="39" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C73" s="40" t="inlineStr">
         <is>
-          <t>BELFB</t>
+          <t>WTTR</t>
         </is>
       </c>
       <c r="D73" s="40" t="inlineStr">
         <is>
-          <t>Bel Fuse Inc. Class B</t>
+          <t>Select Water Solutions, Inc. Class A</t>
         </is>
       </c>
       <c r="E73" s="40" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F73" s="41" t="n">
-        <v>113.7309</v>
+        <v>61.8429</v>
       </c>
       <c r="G73" s="40" t="inlineStr">
         <is>
@@ -59437,12 +59857,12 @@
       </c>
       <c r="H73" s="40" t="inlineStr">
         <is>
-          <t>stop is 0.83x ATR (multiples of a normal day's swing) (22.1602)</t>
+          <t>stop is 14.1% away</t>
         </is>
       </c>
       <c r="I73" s="40" t="inlineStr">
         <is>
-          <t>stop is 0.83x ATR (22.1602) - inside daily noise, it gets hit by nothing happening (floor 1.0x)</t>
+          <t>stop is 14.1% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
         </is>
       </c>
       <c r="J73" s="40" t="inlineStr"/>
@@ -59453,25 +59873,25 @@
         <v>73</v>
       </c>
       <c r="B74" s="39" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C74" s="40" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>XLI</t>
         </is>
       </c>
       <c r="D74" s="40" t="inlineStr">
         <is>
-          <t>Wall Street Cash</t>
+          <t>State Street Industrial Select Sector SPDR ETF</t>
         </is>
       </c>
       <c r="E74" s="40" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F74" s="41" t="n">
-        <v>142.3284</v>
+        <v>113.9258</v>
       </c>
       <c r="G74" s="40" t="inlineStr">
         <is>
@@ -59480,41 +59900,41 @@
       </c>
       <c r="H74" s="40" t="inlineStr">
         <is>
-          <t>stop is 0.98x ATR (multiples of a normal day's swing) (816.7811)</t>
+          <t>trend strength (ADX) 17.1885 below 20</t>
         </is>
       </c>
       <c r="I74" s="40" t="inlineStr">
         <is>
-          <t>stop is 0.98x ATR (816.7811) - inside daily noise, it gets hit by nothing happening (floor 1.0x)</t>
+          <t>trend strength (ADX) 17.1885 below 20 - no trend to ride; stop is 1.00x ATR (3.7609) - inside daily noise, it gets hit by no...</t>
         </is>
       </c>
       <c r="J74" s="40" t="inlineStr"/>
       <c r="K74" s="40" t="inlineStr"/>
     </row>
-    <row r="75" ht="30" customHeight="1">
+    <row r="75" ht="45" customHeight="1">
       <c r="A75" s="38" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="39" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C75" s="40" t="inlineStr">
         <is>
-          <t>HNGE</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="D75" s="40" t="inlineStr">
         <is>
-          <t>Hinge Health, Inc. Class A</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="E75" s="40" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F75" s="41" t="n">
-        <v>55.7869</v>
+        <v>106.4091</v>
       </c>
       <c r="G75" s="40" t="inlineStr">
         <is>
@@ -59523,55 +59943,55 @@
       </c>
       <c r="H75" s="40" t="inlineStr">
         <is>
-          <t>stop is 13.5% away</t>
+          <t>price 274.6025 at/below its trend line (ZLSMA) 276.6194</t>
         </is>
       </c>
       <c r="I75" s="40" t="inlineStr">
         <is>
-          <t>stop is 13.5% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
+          <t>price 274.6025 at/below its trend line (ZLSMA) 276.6194 - structure has not turned; stop is 0.85x ATR (multiples of a normal day's swing) (13.1266) - inside dai...</t>
         </is>
       </c>
       <c r="J75" s="40" t="inlineStr"/>
       <c r="K75" s="40" t="inlineStr"/>
     </row>
-    <row r="76" ht="45" customHeight="1">
+    <row r="76" ht="30" customHeight="1">
       <c r="A76" s="38" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="39" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C76" s="40" t="inlineStr">
         <is>
-          <t>HNST</t>
+          <t>CENX</t>
         </is>
       </c>
       <c r="D76" s="40" t="inlineStr">
         <is>
-          <t>Honest Company, Inc.</t>
+          <t>Century Aluminum Company</t>
         </is>
       </c>
       <c r="E76" s="40" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F76" s="41" t="n">
-        <v>356.2927</v>
+        <v>225.0662</v>
       </c>
       <c r="G76" s="40" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>REPAIR</t>
         </is>
       </c>
       <c r="H76" s="40" t="inlineStr">
         <is>
-          <t>stop is 6.64x ATR (multiples of a normal day's swing)</t>
+          <t>stop is 15.3% away</t>
         </is>
       </c>
       <c r="I76" s="40" t="inlineStr">
         <is>
-          <t>stop is 6.64x ATR (multiples of a normal day's swing) - so wide the position shrinks to a token (ceiling 4.0x); stop is 36.3% away - volatility...</t>
+          <t>stop is 15.3% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
         </is>
       </c>
       <c r="J76" s="40" t="inlineStr"/>
@@ -59582,25 +60002,25 @@
         <v>76</v>
       </c>
       <c r="B77" s="39" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C77" s="40" t="inlineStr">
         <is>
-          <t>NOVT</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="D77" s="40" t="inlineStr">
         <is>
-          <t>Novanta Inc</t>
+          <t>Energy Transfer LP</t>
         </is>
       </c>
       <c r="E77" s="40" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F77" s="41" t="n">
-        <v>208.7503</v>
+        <v>-26.4282</v>
       </c>
       <c r="G77" s="40" t="inlineStr">
         <is>
@@ -59609,12 +60029,12 @@
       </c>
       <c r="H77" s="40" t="inlineStr">
         <is>
-          <t>stop is 12.4% away</t>
+          <t>price 20.2188 at/below its trend line (ZLSMA) 21.2118</t>
         </is>
       </c>
       <c r="I77" s="40" t="inlineStr">
         <is>
-          <t>stop is 12.4% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
+          <t>price 20.2188 at/below its trend line (ZLSMA) 21.2118 - structure has not turned</t>
         </is>
       </c>
       <c r="J77" s="40" t="inlineStr"/>
@@ -59625,110 +60045,102 @@
         <v>77</v>
       </c>
       <c r="B78" s="39" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C78" s="40" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D78" s="40" t="inlineStr">
         <is>
-          <t>Natera, Inc.</t>
+          <t>First Solar, Inc.</t>
         </is>
       </c>
       <c r="E78" s="40" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F78" s="41" t="n">
-        <v>425.2543</v>
+        <v>200.8589</v>
       </c>
       <c r="G78" s="40" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>REPAIR</t>
         </is>
       </c>
       <c r="H78" s="40" t="inlineStr">
         <is>
-          <t>stop is 5.47x ATR (multiples of a normal day's swing)</t>
+          <t>stop is 4.12x ATR (multiples of a normal day's swing)</t>
         </is>
       </c>
       <c r="I78" s="40" t="inlineStr">
         <is>
-          <t>stop is 5.47x ATR (multiples of a normal day's swing) - so wide the position shrinks to a token (ceiling 4.0x); stop is 20.5% away - volatility...</t>
+          <t>stop is 4.12x ATR (multiples of a normal day's swing) - so wide the position shrinks to a token (ceiling 4.0x); stop is 22.1% away - volatility...</t>
         </is>
       </c>
       <c r="J78" s="40" t="inlineStr"/>
       <c r="K78" s="40" t="inlineStr"/>
     </row>
-    <row r="79" ht="45" customHeight="1">
+    <row r="79" ht="30" customHeight="1">
       <c r="A79" s="38" t="n">
         <v>78</v>
       </c>
       <c r="B79" s="39" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C79" s="40" t="inlineStr">
         <is>
-          <t>PCVX</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="D79" s="40" t="inlineStr">
         <is>
-          <t>Vaxcyte, Inc.</t>
+          <t>Innodata Inc.</t>
         </is>
       </c>
       <c r="E79" s="40" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F79" s="41" t="n">
-        <v>193.9287</v>
+        <v>120.0567</v>
       </c>
       <c r="G79" s="40" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>REPAIR</t>
         </is>
       </c>
       <c r="H79" s="40" t="inlineStr">
         <is>
-          <t>stop is 12.3% away</t>
+          <t>stop is 16.9% away</t>
         </is>
       </c>
       <c r="I79" s="40" t="inlineStr">
         <is>
-          <t>stop is 12.3% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
-        </is>
-      </c>
-      <c r="J79" s="40" t="inlineStr">
-        <is>
-          <t>Trial readout ~2027-03 (window)</t>
-        </is>
-      </c>
-      <c r="K79" s="40" t="inlineStr">
-        <is>
-          <t>Ph3 readout window ~2027-03. BINARY - can gap +/-50%. Do NOT hold a momentum long through it; awareness / defined-risk spec only, sized for total loss.</t>
-        </is>
-      </c>
+          <t>stop is 16.9% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
+        </is>
+      </c>
+      <c r="J79" s="40" t="inlineStr"/>
+      <c r="K79" s="40" t="inlineStr"/>
     </row>
     <row r="80" ht="45" customHeight="1">
       <c r="A80" s="38" t="n">
         <v>79</v>
       </c>
       <c r="B80" s="39" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C80" s="40" t="inlineStr">
         <is>
-          <t>PRLB</t>
+          <t>MATX</t>
         </is>
       </c>
       <c r="D80" s="40" t="inlineStr">
         <is>
-          <t>Proto Labs, Inc.</t>
+          <t>Matson, Inc.</t>
         </is>
       </c>
       <c r="E80" s="40" t="inlineStr">
@@ -59737,7 +60149,7 @@
         </is>
       </c>
       <c r="F80" s="41" t="n">
-        <v>172.2101</v>
+        <v>-47.962</v>
       </c>
       <c r="G80" s="40" t="inlineStr">
         <is>
@@ -59746,65 +60158,65 @@
       </c>
       <c r="H80" s="40" t="inlineStr">
         <is>
-          <t>stop is 0.85x ATR (multiples of a normal day's swing) (5.17)</t>
+          <t>price 206.475 at/below its trend line (ZLSMA) 211.6074</t>
         </is>
       </c>
       <c r="I80" s="40" t="inlineStr">
         <is>
-          <t>stop is 0.85x ATR (5.17) - inside daily noise, it gets hit by nothing happening (floor 1.0x)</t>
+          <t>price 206.475 at/below its trend line (ZLSMA) 211.6074 - structure has not turned; stop is 0.80x ATR (multiples of a normal day's swing) (9.848) - inside daily ...</t>
         </is>
       </c>
       <c r="J80" s="40" t="inlineStr"/>
       <c r="K80" s="40" t="inlineStr"/>
     </row>
-    <row r="81" ht="45" customHeight="1">
+    <row r="81" ht="60" customHeight="1">
       <c r="A81" s="38" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="39" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C81" s="40" t="inlineStr">
         <is>
-          <t>RYTM</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="D81" s="40" t="inlineStr">
         <is>
-          <t>Rhythm Pharmaceuticals, Inc.</t>
+          <t>Rocket Lab Corporation</t>
         </is>
       </c>
       <c r="E81" s="40" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F81" s="41" t="n">
-        <v>214.4017</v>
+        <v>140.8987</v>
       </c>
       <c r="G81" s="40" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>REPAIR</t>
         </is>
       </c>
       <c r="H81" s="40" t="inlineStr">
         <is>
-          <t>stop is 13.5% away</t>
+          <t>stop is 23.7% away</t>
         </is>
       </c>
       <c r="I81" s="40" t="inlineStr">
         <is>
-          <t>stop is 13.5% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
+          <t>stop is 23.7% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
         </is>
       </c>
       <c r="J81" s="40" t="inlineStr">
         <is>
-          <t>Trial readout ~2027-03-13 (window)</t>
+          <t>Earnings 2026-08-10</t>
         </is>
       </c>
       <c r="K81" s="40" t="inlineStr">
         <is>
-          <t>Ph3 readout window ~2027-03-13. BINARY - can gap +/-50%. Do NOT hold a momentum long through it; awareness / defined-risk spec only, sized for total loss.</t>
+          <t>Reports 2026-08-10 (est EPS -0.06). If long &amp; extended, TRIM into the print - do NOT hold full size through a binary. Fresh entry only POST-print if it beats AND holds the gap (PEAD drift = our one measured edge); else awareness-only.</t>
         </is>
       </c>
     </row>
@@ -59813,25 +60225,25 @@
         <v>81</v>
       </c>
       <c r="B82" s="39" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C82" s="40" t="inlineStr">
         <is>
-          <t>SRRK</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D82" s="40" t="inlineStr">
         <is>
-          <t>Scholar Rock Holding Corp.</t>
+          <t>SentinelOne, Inc. Class A</t>
         </is>
       </c>
       <c r="E82" s="40" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F82" s="41" t="n">
-        <v>73.3227</v>
+        <v>157.2875</v>
       </c>
       <c r="G82" s="40" t="inlineStr">
         <is>
@@ -59840,12 +60252,12 @@
       </c>
       <c r="H82" s="40" t="inlineStr">
         <is>
-          <t>stop is 16.2% away</t>
+          <t>price 21.2946 at/below its trend line (ZLSMA) 21.6135</t>
         </is>
       </c>
       <c r="I82" s="40" t="inlineStr">
         <is>
-          <t>stop is 16.2% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
+          <t>price 21.2946 at/below its trend line (ZLSMA) 21.6135 - structure has not turned</t>
         </is>
       </c>
       <c r="J82" s="40" t="inlineStr"/>
@@ -59860,21 +60272,21 @@
       </c>
       <c r="C83" s="40" t="inlineStr">
         <is>
-          <t>TWST</t>
+          <t>HNGE</t>
         </is>
       </c>
       <c r="D83" s="40" t="inlineStr">
         <is>
-          <t>Twist Bioscience Corp.</t>
+          <t>Hinge Health, Inc. Class A</t>
         </is>
       </c>
       <c r="E83" s="40" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F83" s="41" t="n">
-        <v>213.5701</v>
+        <v>55.7869</v>
       </c>
       <c r="G83" s="40" t="inlineStr">
         <is>
@@ -59883,18 +60295,18 @@
       </c>
       <c r="H83" s="40" t="inlineStr">
         <is>
-          <t>stop is 19.4% away</t>
+          <t>stop is 13.5% away</t>
         </is>
       </c>
       <c r="I83" s="40" t="inlineStr">
         <is>
-          <t>stop is 19.4% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
+          <t>stop is 13.5% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
         </is>
       </c>
       <c r="J83" s="40" t="inlineStr"/>
       <c r="K83" s="40" t="inlineStr"/>
     </row>
-    <row r="84" ht="45" customHeight="1">
+    <row r="84" ht="30" customHeight="1">
       <c r="A84" s="38" t="n">
         <v>83</v>
       </c>
@@ -59903,21 +60315,21 @@
       </c>
       <c r="C84" s="40" t="inlineStr">
         <is>
-          <t>URGN</t>
+          <t>NOVT</t>
         </is>
       </c>
       <c r="D84" s="40" t="inlineStr">
         <is>
-          <t>UroGen Pharma Ltd.</t>
+          <t>Novanta Inc</t>
         </is>
       </c>
       <c r="E84" s="40" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F84" s="41" t="n">
-        <v>220.2193</v>
+        <v>208.7503</v>
       </c>
       <c r="G84" s="40" t="inlineStr">
         <is>
@@ -59926,24 +60338,16 @@
       </c>
       <c r="H84" s="40" t="inlineStr">
         <is>
-          <t>stop is 17.5% away</t>
+          <t>stop is 12.4% away</t>
         </is>
       </c>
       <c r="I84" s="40" t="inlineStr">
         <is>
-          <t>stop is 17.5% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
-        </is>
-      </c>
-      <c r="J84" s="40" t="inlineStr">
-        <is>
-          <t>Trial readout ~2027-03 (window)</t>
-        </is>
-      </c>
-      <c r="K84" s="40" t="inlineStr">
-        <is>
-          <t>Ph3 readout window ~2027-03. BINARY - can gap +/-50%. Do NOT hold a momentum long through it; awareness / defined-risk spec only, sized for total loss.</t>
-        </is>
-      </c>
+          <t>stop is 12.4% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
+        </is>
+      </c>
+      <c r="J84" s="40" t="inlineStr"/>
+      <c r="K84" s="40" t="inlineStr"/>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="38" t="n">
@@ -59954,12 +60358,12 @@
       </c>
       <c r="C85" s="40" t="inlineStr">
         <is>
-          <t>VSEC</t>
+          <t>TWST</t>
         </is>
       </c>
       <c r="D85" s="40" t="inlineStr">
         <is>
-          <t>VSE Corporation</t>
+          <t>Twist Bioscience Corp.</t>
         </is>
       </c>
       <c r="E85" s="40" t="inlineStr">
@@ -59968,7 +60372,7 @@
         </is>
       </c>
       <c r="F85" s="41" t="n">
-        <v>169.8721</v>
+        <v>213.5701</v>
       </c>
       <c r="G85" s="40" t="inlineStr">
         <is>
@@ -59977,18 +60381,18 @@
       </c>
       <c r="H85" s="40" t="inlineStr">
         <is>
-          <t>stop is 12.4% away</t>
+          <t>stop is 19.4% away</t>
         </is>
       </c>
       <c r="I85" s="40" t="inlineStr">
         <is>
-          <t>stop is 12.4% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
+          <t>stop is 19.4% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
         </is>
       </c>
       <c r="J85" s="40" t="inlineStr"/>
       <c r="K85" s="40" t="inlineStr"/>
     </row>
-    <row r="86" ht="30" customHeight="1">
+    <row r="86" ht="45" customHeight="1">
       <c r="A86" s="38" t="n">
         <v>85</v>
       </c>
@@ -59997,12 +60401,12 @@
       </c>
       <c r="C86" s="40" t="inlineStr">
         <is>
-          <t>WTTR</t>
+          <t>URGN</t>
         </is>
       </c>
       <c r="D86" s="40" t="inlineStr">
         <is>
-          <t>Select Water Solutions, Inc. Class A</t>
+          <t>UroGen Pharma Ltd.</t>
         </is>
       </c>
       <c r="E86" s="40" t="inlineStr">
@@ -60011,7 +60415,7 @@
         </is>
       </c>
       <c r="F86" s="41" t="n">
-        <v>61.8429</v>
+        <v>220.2193</v>
       </c>
       <c r="G86" s="40" t="inlineStr">
         <is>
@@ -60020,16 +60424,24 @@
       </c>
       <c r="H86" s="40" t="inlineStr">
         <is>
-          <t>stop is 14.1% away</t>
+          <t>stop is 17.5% away</t>
         </is>
       </c>
       <c r="I86" s="40" t="inlineStr">
         <is>
-          <t>stop is 14.1% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
-        </is>
-      </c>
-      <c r="J86" s="40" t="inlineStr"/>
-      <c r="K86" s="40" t="inlineStr"/>
+          <t>stop is 17.5% away - volatility cap 12%: a name this wild shrinks a fixed-risk position to a token</t>
+        </is>
+      </c>
+      <c r="J86" s="40" t="inlineStr">
+        <is>
+          <t>Trial readout ~2027-03 (window)</t>
+        </is>
+      </c>
+      <c r="K86" s="40" t="inlineStr">
+        <is>
+          <t>Ph3 readout window ~2027-03. BINARY - can gap +/-50%. Do NOT hold a momentum long through it; awareness / defined-risk spec only, sized for total loss.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
@@ -60193,7 +60605,7 @@
       <c r="L2" s="26" t="inlineStr"/>
       <c r="M2" s="26" t="inlineStr"/>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3" ht="45" customHeight="1">
       <c r="A3" s="24" t="n">
         <v>2</v>
       </c>
@@ -60230,7 +60642,7 @@
       </c>
       <c r="K3" s="26" t="inlineStr">
         <is>
-          <t>no specific flag - still unvalidated</t>
+          <t>trend-strength reading (ADX) is only 24 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L3" s="26" t="inlineStr"/>
@@ -60330,7 +60742,7 @@
       <c r="L5" s="26" t="inlineStr"/>
       <c r="M5" s="26" t="inlineStr"/>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="45" customHeight="1">
       <c r="A6" s="24" t="n">
         <v>5</v>
       </c>
@@ -60367,7 +60779,7 @@
       </c>
       <c r="K6" s="26" t="inlineStr">
         <is>
-          <t>no specific flag - still unvalidated</t>
+          <t>trend-strength reading (ADX) is only 21 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L6" s="26" t="inlineStr"/>
@@ -60545,7 +60957,7 @@
       <c r="L10" s="26" t="inlineStr"/>
       <c r="M10" s="26" t="inlineStr"/>
     </row>
-    <row r="11" ht="15" customHeight="1">
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="24" t="n">
         <v>10</v>
       </c>
@@ -60582,13 +60994,13 @@
       </c>
       <c r="K11" s="26" t="inlineStr">
         <is>
-          <t>no specific flag - still unvalidated</t>
+          <t>trend-strength reading (ADX) is only 22 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L11" s="26" t="inlineStr"/>
       <c r="M11" s="26" t="inlineStr"/>
     </row>
-    <row r="12" ht="15" customHeight="1">
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="17" t="n">
         <v>11</v>
       </c>
@@ -60625,7 +61037,7 @@
       </c>
       <c r="K12" s="19" t="inlineStr">
         <is>
-          <t>no specific flag - still unvalidated</t>
+          <t>trend-strength reading (ADX) is only 21 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L12" s="19" t="inlineStr"/>
@@ -60717,7 +61129,7 @@
       <c r="L14" s="19" t="inlineStr"/>
       <c r="M14" s="19" t="inlineStr"/>
     </row>
-    <row r="15" ht="30" customHeight="1">
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="17" t="n">
         <v>14</v>
       </c>
@@ -60754,7 +61166,7 @@
       </c>
       <c r="K15" s="19" t="inlineStr">
         <is>
-          <t>price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>trend-strength reading (ADX) is only 21 - no real trend, and shorting a sideways chop bleeds money; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
         </is>
       </c>
       <c r="L15" s="19" t="inlineStr"/>
@@ -61018,7 +61430,7 @@
       <c r="L21" s="19" t="inlineStr"/>
       <c r="M21" s="19" t="inlineStr"/>
     </row>
-    <row r="22" ht="15" customHeight="1">
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="17" t="n">
         <v>21</v>
       </c>
@@ -61055,7 +61467,7 @@
       </c>
       <c r="K22" s="19" t="inlineStr">
         <is>
-          <t>no specific flag - still unvalidated</t>
+          <t>trend-strength reading (ADX) is only 21 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L22" s="19" t="inlineStr"/>
@@ -61233,7 +61645,7 @@
       <c r="L26" s="19" t="inlineStr"/>
       <c r="M26" s="19" t="inlineStr"/>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27" ht="45" customHeight="1">
       <c r="A27" s="17" t="n">
         <v>26</v>
       </c>
@@ -61270,7 +61682,7 @@
       </c>
       <c r="K27" s="19" t="inlineStr">
         <is>
-          <t>no specific flag - still unvalidated</t>
+          <t>trend-strength reading (ADX) is only 22 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L27" s="19" t="inlineStr"/>
@@ -61413,7 +61825,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="17" t="n">
         <v>30</v>
       </c>
@@ -61450,7 +61862,7 @@
       </c>
       <c r="K31" s="19" t="inlineStr">
         <is>
-          <t>price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>trend-strength reading (ADX) is only 27 - no real trend, and shorting a sideways chop bleeds money; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
         </is>
       </c>
       <c r="L31" s="19" t="inlineStr"/>
@@ -61536,13 +61948,13 @@
       </c>
       <c r="K33" s="19" t="inlineStr">
         <is>
-          <t>price is ABOVE its trend line (ZLSMA) - the structure has not broken down; thinly traded (about $2,309,222 a day) - shares are hard to borrow and a squeeze moves it violently</t>
+          <t>trend-strength reading (ADX) is only 25 - no real trend, and shorting a sideways chop bleeds money; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
         </is>
       </c>
       <c r="L33" s="19" t="inlineStr"/>
       <c r="M33" s="19" t="inlineStr"/>
     </row>
-    <row r="34" ht="30" customHeight="1">
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="17" t="n">
         <v>33</v>
       </c>
@@ -61579,13 +61991,13 @@
       </c>
       <c r="K34" s="19" t="inlineStr">
         <is>
-          <t>still +2.6% ABOVE its 200-day average - this is not actually a downtrend</t>
+          <t>still +2.6% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 26 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L34" s="19" t="inlineStr"/>
       <c r="M34" s="19" t="inlineStr"/>
     </row>
-    <row r="35" ht="15" customHeight="1">
+    <row r="35" ht="45" customHeight="1">
       <c r="A35" s="17" t="n">
         <v>34</v>
       </c>
@@ -61622,7 +62034,7 @@
       </c>
       <c r="K35" s="19" t="inlineStr">
         <is>
-          <t>no specific flag - still unvalidated</t>
+          <t>trend-strength reading (ADX) is only 21 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L35" s="19" t="inlineStr"/>
@@ -61671,7 +62083,7 @@
       <c r="L36" s="19" t="inlineStr"/>
       <c r="M36" s="19" t="inlineStr"/>
     </row>
-    <row r="37" ht="15" customHeight="1">
+    <row r="37" ht="45" customHeight="1">
       <c r="A37" s="17" t="n">
         <v>36</v>
       </c>
@@ -61708,7 +62120,7 @@
       </c>
       <c r="K37" s="19" t="inlineStr">
         <is>
-          <t>no specific flag - still unvalidated</t>
+          <t>trend-strength reading (ADX) is only 25 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L37" s="19" t="inlineStr"/>
@@ -61757,7 +62169,7 @@
       <c r="L38" s="19" t="inlineStr"/>
       <c r="M38" s="19" t="inlineStr"/>
     </row>
-    <row r="39" ht="30" customHeight="1">
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="17" t="n">
         <v>38</v>
       </c>
@@ -61794,7 +62206,7 @@
       </c>
       <c r="K39" s="19" t="inlineStr">
         <is>
-          <t>price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>trend-strength reading (ADX) is only 26 - no real trend, and shorting a sideways chop bleeds money; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
         </is>
       </c>
       <c r="L39" s="19" t="inlineStr"/>
@@ -61880,7 +62292,7 @@
       </c>
       <c r="K41" s="19" t="inlineStr">
         <is>
-          <t>price is ABOVE its trend line (ZLSMA) - the structure has not broken down; thinly traded (about $5,633,610 a day) - shares are hard to borrow and a squeeze moves it violently</t>
+          <t>trend-strength reading (ADX) is only 25 - no real trend, and shorting a sideways chop bleeds money; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
         </is>
       </c>
       <c r="L41" s="19" t="inlineStr"/>
@@ -61972,7 +62384,7 @@
       <c r="L43" s="19" t="inlineStr"/>
       <c r="M43" s="19" t="inlineStr"/>
     </row>
-    <row r="44" ht="30" customHeight="1">
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" s="17" t="n">
         <v>43</v>
       </c>
@@ -62009,7 +62421,7 @@
       </c>
       <c r="K44" s="19" t="inlineStr">
         <is>
-          <t>still +13.6% ABOVE its 200-day average - this is not actually a downtrend</t>
+          <t>still +13.6% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 23 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L44" s="19" t="inlineStr"/>
@@ -62101,7 +62513,7 @@
       <c r="L46" s="19" t="inlineStr"/>
       <c r="M46" s="19" t="inlineStr"/>
     </row>
-    <row r="47" ht="30" customHeight="1">
+    <row r="47" ht="60" customHeight="1">
       <c r="A47" s="17" t="n">
         <v>46</v>
       </c>
@@ -62138,7 +62550,7 @@
       </c>
       <c r="K47" s="19" t="inlineStr">
         <is>
-          <t>still +16.8% ABOVE its 200-day average - this is not actually a downtrend</t>
+          <t>still +16.8% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 24 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L47" s="19" t="inlineStr"/>
@@ -62230,7 +62642,7 @@
       <c r="L49" s="19" t="inlineStr"/>
       <c r="M49" s="19" t="inlineStr"/>
     </row>
-    <row r="50" ht="30" customHeight="1">
+    <row r="50" ht="60" customHeight="1">
       <c r="A50" s="17" t="n">
         <v>49</v>
       </c>
@@ -62267,7 +62679,7 @@
       </c>
       <c r="K50" s="19" t="inlineStr">
         <is>
-          <t>still +7.2% ABOVE its 200-day average - this is not actually a downtrend</t>
+          <t>still +7.2% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 22 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L50" s="19" t="inlineStr"/>
@@ -62359,7 +62771,7 @@
       <c r="L52" s="19" t="inlineStr"/>
       <c r="M52" s="19" t="inlineStr"/>
     </row>
-    <row r="53" ht="30" customHeight="1">
+    <row r="53" ht="60" customHeight="1">
       <c r="A53" s="17" t="n">
         <v>52</v>
       </c>
@@ -62396,7 +62808,7 @@
       </c>
       <c r="K53" s="19" t="inlineStr">
         <is>
-          <t>still +11.8% ABOVE its 200-day average - this is not actually a downtrend</t>
+          <t>still +11.8% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 25 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L53" s="19" t="inlineStr"/>
@@ -62445,7 +62857,7 @@
       <c r="L54" s="19" t="inlineStr"/>
       <c r="M54" s="19" t="inlineStr"/>
     </row>
-    <row r="55" ht="30" customHeight="1">
+    <row r="55" ht="60" customHeight="1">
       <c r="A55" s="17" t="n">
         <v>54</v>
       </c>
@@ -62482,13 +62894,13 @@
       </c>
       <c r="K55" s="19" t="inlineStr">
         <is>
-          <t>price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>trend-strength reading (ADX) is only 23 - no real trend, and shorting a sideways chop bleeds money; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
         </is>
       </c>
       <c r="L55" s="19" t="inlineStr"/>
       <c r="M55" s="19" t="inlineStr"/>
     </row>
-    <row r="56" ht="30" customHeight="1">
+    <row r="56" ht="60" customHeight="1">
       <c r="A56" s="17" t="n">
         <v>55</v>
       </c>
@@ -62525,7 +62937,7 @@
       </c>
       <c r="K56" s="19" t="inlineStr">
         <is>
-          <t>buyers are in control (buying pressure 22) - wrong side to be short</t>
+          <t>trend-strength reading (ADX) is only 23 - no real trend, and shorting a sideways chop bleeds money; buyers are in control (buying pressure 22) - wrong side to be short</t>
         </is>
       </c>
       <c r="L56" s="19" t="inlineStr"/>
@@ -62617,7 +63029,7 @@
       <c r="L58" s="19" t="inlineStr"/>
       <c r="M58" s="19" t="inlineStr"/>
     </row>
-    <row r="59" ht="30" customHeight="1">
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="17" t="n">
         <v>58</v>
       </c>
@@ -62654,7 +63066,7 @@
       </c>
       <c r="K59" s="19" t="inlineStr">
         <is>
-          <t>still +6.3% ABOVE its 200-day average - this is not actually a downtrend</t>
+          <t>still +6.3% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 25 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L59" s="19" t="inlineStr"/>
@@ -62783,7 +63195,7 @@
       </c>
       <c r="K62" s="19" t="inlineStr">
         <is>
-          <t>still +6.8% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 19) - wrong side to be short</t>
+          <t>still +6.8% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 25 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L62" s="19" t="inlineStr"/>
@@ -62832,7 +63244,7 @@
       <c r="L63" s="19" t="inlineStr"/>
       <c r="M63" s="19" t="inlineStr"/>
     </row>
-    <row r="64" ht="30" customHeight="1">
+    <row r="64" ht="60" customHeight="1">
       <c r="A64" s="17" t="n">
         <v>63</v>
       </c>
@@ -62869,7 +63281,7 @@
       </c>
       <c r="K64" s="19" t="inlineStr">
         <is>
-          <t>still +8.1% ABOVE its 200-day average - this is not actually a downtrend</t>
+          <t>still +8.1% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 24 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L64" s="19" t="inlineStr"/>
@@ -62926,7 +63338,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
+    <row r="66" ht="60" customHeight="1">
       <c r="A66" s="17" t="n">
         <v>65</v>
       </c>
@@ -62963,7 +63375,7 @@
       </c>
       <c r="K66" s="19" t="inlineStr">
         <is>
-          <t>price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>trend-strength reading (ADX) is only 26 - no real trend, and shorting a sideways chop bleeds money; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
         </is>
       </c>
       <c r="L66" s="19" t="inlineStr"/>
@@ -63012,7 +63424,7 @@
       <c r="L67" s="19" t="inlineStr"/>
       <c r="M67" s="19" t="inlineStr"/>
     </row>
-    <row r="68" ht="30" customHeight="1">
+    <row r="68" ht="60" customHeight="1">
       <c r="A68" s="17" t="n">
         <v>67</v>
       </c>
@@ -63049,7 +63461,7 @@
       </c>
       <c r="K68" s="19" t="inlineStr">
         <is>
-          <t>still +18.9% ABOVE its 200-day average - this is not actually a downtrend</t>
+          <t>still +18.9% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 21 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L68" s="19" t="inlineStr"/>
@@ -63184,7 +63596,7 @@
       <c r="L71" s="19" t="inlineStr"/>
       <c r="M71" s="19" t="inlineStr"/>
     </row>
-    <row r="72" ht="30" customHeight="1">
+    <row r="72" ht="60" customHeight="1">
       <c r="A72" s="17" t="n">
         <v>71</v>
       </c>
@@ -63221,7 +63633,7 @@
       </c>
       <c r="K72" s="19" t="inlineStr">
         <is>
-          <t>still +4.4% ABOVE its 200-day average - this is not actually a downtrend</t>
+          <t>still +4.4% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 24 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L72" s="19" t="inlineStr"/>
@@ -63313,7 +63725,7 @@
       <c r="L74" s="19" t="inlineStr"/>
       <c r="M74" s="19" t="inlineStr"/>
     </row>
-    <row r="75" ht="30" customHeight="1">
+    <row r="75" ht="60" customHeight="1">
       <c r="A75" s="17" t="n">
         <v>74</v>
       </c>
@@ -63350,7 +63762,7 @@
       </c>
       <c r="K75" s="19" t="inlineStr">
         <is>
-          <t>still +14.9% ABOVE its 200-day average - this is not actually a downtrend</t>
+          <t>still +14.9% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 25 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L75" s="19" t="inlineStr"/>
@@ -63436,13 +63848,13 @@
       </c>
       <c r="K77" s="19" t="inlineStr">
         <is>
-          <t>still +19.8% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 15) - wrong side to be short</t>
+          <t>still +19.8% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 25 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L77" s="19" t="inlineStr"/>
       <c r="M77" s="19" t="inlineStr"/>
     </row>
-    <row r="78" ht="30" customHeight="1">
+    <row r="78" ht="60" customHeight="1">
       <c r="A78" s="17" t="n">
         <v>77</v>
       </c>
@@ -63479,7 +63891,7 @@
       </c>
       <c r="K78" s="19" t="inlineStr">
         <is>
-          <t>still +9.7% ABOVE its 200-day average - this is not actually a downtrend</t>
+          <t>still +9.7% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 22 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L78" s="19" t="inlineStr"/>
@@ -63708,7 +64120,7 @@
       <c r="L83" s="19" t="inlineStr"/>
       <c r="M83" s="19" t="inlineStr"/>
     </row>
-    <row r="84" ht="30" customHeight="1">
+    <row r="84" ht="60" customHeight="1">
       <c r="A84" s="17" t="n">
         <v>83</v>
       </c>
@@ -63745,7 +64157,7 @@
       </c>
       <c r="K84" s="19" t="inlineStr">
         <is>
-          <t>still +16.7% ABOVE its 200-day average - this is not actually a downtrend</t>
+          <t>still +16.7% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 22 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L84" s="19" t="inlineStr"/>
@@ -64132,7 +64544,7 @@
       </c>
       <c r="K93" s="19" t="inlineStr">
         <is>
-          <t>still +52.7% ABOVE its 200-day average - this is not actually a downtrend; thinly traded (about $16,588,112 a day) - shares are hard to borrow and a squeeze moves it violently</t>
+          <t>still +52.7% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 27 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L93" s="19" t="inlineStr">
@@ -64146,7 +64558,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="30" customHeight="1">
+    <row r="94" ht="60" customHeight="1">
       <c r="A94" s="17" t="n">
         <v>93</v>
       </c>
@@ -64183,7 +64595,7 @@
       </c>
       <c r="K94" s="19" t="inlineStr">
         <is>
-          <t>still +12.6% ABOVE its 200-day average - this is not actually a downtrend</t>
+          <t>still +12.6% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 20 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L94" s="19" t="inlineStr"/>
@@ -64269,7 +64681,7 @@
       </c>
       <c r="K96" s="19" t="inlineStr">
         <is>
-          <t>still +5.9% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 20) - wrong side to be short</t>
+          <t>still +5.9% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 26 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L96" s="19" t="inlineStr"/>
@@ -64312,7 +64724,7 @@
       </c>
       <c r="K97" s="19" t="inlineStr">
         <is>
-          <t>still +12.0% ABOVE its 200-day average - this is not actually a downtrend</t>
+          <t>still +12.0% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 22 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L97" s="19" t="inlineStr">
@@ -64326,7 +64738,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="30" customHeight="1">
+    <row r="98" ht="60" customHeight="1">
       <c r="A98" s="17" t="n">
         <v>97</v>
       </c>
@@ -64363,7 +64775,7 @@
       </c>
       <c r="K98" s="19" t="inlineStr">
         <is>
-          <t>still +1.6% ABOVE its 200-day average - this is not actually a downtrend</t>
+          <t>still +1.6% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 24 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L98" s="19" t="inlineStr"/>
@@ -64449,7 +64861,7 @@
       </c>
       <c r="K100" s="19" t="inlineStr">
         <is>
-          <t>still +10.4% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 21) - wrong side to be short</t>
+          <t>still +10.4% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 23 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L100" s="19" t="inlineStr"/>
@@ -64498,7 +64910,7 @@
       <c r="L101" s="19" t="inlineStr"/>
       <c r="M101" s="19" t="inlineStr"/>
     </row>
-    <row r="102" ht="30" customHeight="1">
+    <row r="102" ht="60" customHeight="1">
       <c r="A102" s="17" t="n">
         <v>101</v>
       </c>
@@ -64535,7 +64947,7 @@
       </c>
       <c r="K102" s="19" t="inlineStr">
         <is>
-          <t>still +3.4% ABOVE its 200-day average - this is not actually a downtrend</t>
+          <t>still +3.4% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 22 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L102" s="19" t="inlineStr"/>
@@ -64887,7 +65299,7 @@
       </c>
       <c r="K110" s="19" t="inlineStr">
         <is>
-          <t>still +17.9% ABOVE its 200-day average - this is not actually a downtrend; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>still +17.9% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 24 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L110" s="19" t="inlineStr"/>
@@ -64973,7 +65385,7 @@
       </c>
       <c r="K112" s="19" t="inlineStr">
         <is>
-          <t>still +37.4% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 19) - wrong side to be short</t>
+          <t>still +37.4% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 24 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L112" s="19" t="inlineStr"/>
@@ -65016,7 +65428,7 @@
       </c>
       <c r="K113" s="19" t="inlineStr">
         <is>
-          <t>still +5.8% ABOVE its 200-day average - this is not actually a downtrend; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>still +5.8% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 24 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L113" s="19" t="inlineStr"/>
@@ -65059,7 +65471,7 @@
       </c>
       <c r="K114" s="19" t="inlineStr">
         <is>
-          <t>still +7.6% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 18) - wrong side to be short</t>
+          <t>still +7.6% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 21 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L114" s="19" t="inlineStr"/>
@@ -65102,7 +65514,7 @@
       </c>
       <c r="K115" s="19" t="inlineStr">
         <is>
-          <t>still +12.6% ABOVE its 200-day average - this is not actually a downtrend; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>still +12.6% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 24 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L115" s="19" t="inlineStr"/>
@@ -65145,7 +65557,7 @@
       </c>
       <c r="K116" s="19" t="inlineStr">
         <is>
-          <t>still +9.4% ABOVE its 200-day average - this is not actually a downtrend; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>still +9.4% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 22 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L116" s="19" t="inlineStr"/>
@@ -65239,7 +65651,7 @@
       </c>
       <c r="K118" s="19" t="inlineStr">
         <is>
-          <t>still +0.5% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 18) - wrong side to be short</t>
+          <t>still +0.5% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 26 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L118" s="19" t="inlineStr"/>
@@ -65505,7 +65917,7 @@
       </c>
       <c r="K124" s="19" t="inlineStr">
         <is>
-          <t>still +21.2% ABOVE its 200-day average - this is not actually a downtrend; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>still +21.2% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 21 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L124" s="19" t="inlineStr"/>
@@ -65548,7 +65960,7 @@
       </c>
       <c r="K125" s="19" t="inlineStr">
         <is>
-          <t>still +26.7% ABOVE its 200-day average - this is not actually a downtrend; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>still +26.7% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 22 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L125" s="19" t="inlineStr"/>
@@ -65634,7 +66046,7 @@
       </c>
       <c r="K127" s="19" t="inlineStr">
         <is>
-          <t>still +37.4% ABOVE its 200-day average - this is not actually a downtrend; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>still +37.4% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 26 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L127" s="19" t="inlineStr"/>
@@ -65763,7 +66175,7 @@
       </c>
       <c r="K130" s="19" t="inlineStr">
         <is>
-          <t>still +10.4% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 23) - wrong side to be short</t>
+          <t>still +10.4% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 22 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L130" s="19" t="inlineStr"/>
@@ -65892,7 +66304,7 @@
       </c>
       <c r="K133" s="19" t="inlineStr">
         <is>
-          <t>still +13.0% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 22) - wrong side to be short</t>
+          <t>still +13.0% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 22 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L133" s="19" t="inlineStr"/>
@@ -65978,7 +66390,7 @@
       </c>
       <c r="K135" s="19" t="inlineStr">
         <is>
-          <t>still +34.5% ABOVE its 200-day average - this is not actually a downtrend; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>still +34.5% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 24 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L135" s="19" t="inlineStr"/>
@@ -66021,7 +66433,7 @@
       </c>
       <c r="K136" s="19" t="inlineStr">
         <is>
-          <t>still +37.5% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 20) - wrong side to be short</t>
+          <t>still +37.5% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 25 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L136" s="19" t="inlineStr"/>
@@ -66064,7 +66476,7 @@
       </c>
       <c r="K137" s="19" t="inlineStr">
         <is>
-          <t>still +33.3% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 19) - wrong side to be short</t>
+          <t>still +33.3% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 21 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L137" s="19" t="inlineStr"/>
@@ -66244,7 +66656,7 @@
       </c>
       <c r="K141" s="19" t="inlineStr">
         <is>
-          <t>still +54.6% ABOVE its 200-day average - this is not actually a downtrend; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>still +54.6% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 21 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L141" s="19" t="inlineStr"/>
@@ -66287,7 +66699,7 @@
       </c>
       <c r="K142" s="19" t="inlineStr">
         <is>
-          <t>still +4.1% ABOVE its 200-day average - this is not actually a downtrend; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>still +4.1% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 21 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L142" s="19" t="inlineStr"/>
@@ -66416,7 +66828,7 @@
       </c>
       <c r="K145" s="19" t="inlineStr">
         <is>
-          <t>still +4.0% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 23) - wrong side to be short</t>
+          <t>still +4.0% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 20 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L145" s="19" t="inlineStr"/>
@@ -66459,7 +66871,7 @@
       </c>
       <c r="K146" s="19" t="inlineStr">
         <is>
-          <t>still +27.5% ABOVE its 200-day average - this is not actually a downtrend; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>still +27.5% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 25 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L146" s="19" t="inlineStr"/>
@@ -66502,7 +66914,7 @@
       </c>
       <c r="K147" s="19" t="inlineStr">
         <is>
-          <t>still +11.9% ABOVE its 200-day average - this is not actually a downtrend; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>still +11.9% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 21 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L147" s="19" t="inlineStr"/>
@@ -66545,7 +66957,7 @@
       </c>
       <c r="K148" s="19" t="inlineStr">
         <is>
-          <t>still +21.0% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 18) - wrong side to be short</t>
+          <t>still +21.0% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 21 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L148" s="19" t="inlineStr"/>
@@ -66588,7 +67000,7 @@
       </c>
       <c r="K149" s="19" t="inlineStr">
         <is>
-          <t>still +60.9% ABOVE its 200-day average - this is not actually a downtrend; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>still +60.9% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 24 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L149" s="19" t="inlineStr"/>
@@ -66674,7 +67086,7 @@
       </c>
       <c r="K151" s="19" t="inlineStr">
         <is>
-          <t>still +22.4% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 19) - wrong side to be short</t>
+          <t>still +22.4% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 23 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L151" s="19" t="inlineStr"/>
@@ -66717,7 +67129,7 @@
       </c>
       <c r="K152" s="19" t="inlineStr">
         <is>
-          <t>still +65.2% ABOVE its 200-day average - this is not actually a downtrend; price is ABOVE its trend line (ZLSMA) - the structure has not broken down</t>
+          <t>still +65.2% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 22 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L152" s="19" t="inlineStr"/>
@@ -66932,7 +67344,7 @@
       </c>
       <c r="K157" s="19" t="inlineStr">
         <is>
-          <t>still +14.5% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 20) - wrong side to be short</t>
+          <t>still +14.5% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 22 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L157" s="19" t="inlineStr">
@@ -67069,7 +67481,7 @@
       </c>
       <c r="K160" s="19" t="inlineStr">
         <is>
-          <t>still +17.7% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 21) - wrong side to be short</t>
+          <t>still +17.7% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 23 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L160" s="19" t="inlineStr"/>
@@ -67155,7 +67567,7 @@
       </c>
       <c r="K162" s="19" t="inlineStr">
         <is>
-          <t>still +0.3% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 22) - wrong side to be short</t>
+          <t>still +0.3% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 21 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L162" s="19" t="inlineStr"/>
@@ -67241,7 +67653,7 @@
       </c>
       <c r="K164" s="19" t="inlineStr">
         <is>
-          <t>still +15.1% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 21) - wrong side to be short</t>
+          <t>still +15.1% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 23 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L164" s="19" t="inlineStr"/>
@@ -67327,7 +67739,7 @@
       </c>
       <c r="K166" s="19" t="inlineStr">
         <is>
-          <t>still +38.3% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 16) - wrong side to be short</t>
+          <t>still +38.3% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 22 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L166" s="19" t="inlineStr">
@@ -67464,7 +67876,7 @@
       </c>
       <c r="K169" s="19" t="inlineStr">
         <is>
-          <t>still +14.6% ABOVE its 200-day average - this is not actually a downtrend; buyers are in control (buying pressure 18) - wrong side to be short</t>
+          <t>still +14.6% ABOVE its 200-day average - this is not actually a downtrend; trend-strength reading (ADX) is only 22 - no real trend, and shorting a sideways chop bleeds money</t>
         </is>
       </c>
       <c r="L169" s="19" t="inlineStr"/>
@@ -70087,7 +70499,7 @@
       </c>
       <c r="F6" s="19" t="inlineStr">
         <is>
-          <t>(no flags - genuinely clean)</t>
+          <t>* trend-strength reading (ADX) is only 24, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G6" s="19" t="inlineStr">
@@ -70126,7 +70538,7 @@
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>(no flags - genuinely clean)</t>
+          <t>* trend-strength reading (ADX) is only 24, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G7" s="19" t="inlineStr">
@@ -70286,7 +70698,7 @@
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>(no flags - genuinely clean)</t>
+          <t>* trend-strength reading (ADX) is only 22, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -70325,7 +70737,7 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>(no flags - genuinely clean)</t>
+          <t>* trend-strength reading (ADX) is only 24, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G12" s="19" t="inlineStr">
@@ -70446,6 +70858,7 @@
       <c r="F15" s="19" t="inlineStr">
         <is>
           <t>* the stop is 8.7% away, so the position has to shrink to keep the dollar risk at $5k
+* trend-strength reading (ADX) is only 22, under 27 - there is no trend here to ride
 * still repairing - price is +8.2% vs its 200-day average, so starter size only</t>
         </is>
       </c>
@@ -70485,7 +70898,7 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>(no flags - genuinely clean)</t>
+          <t>* trend-strength reading (ADX) is only 25, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
@@ -70526,7 +70939,7 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>(no flags - genuinely clean)</t>
+          <t>* trend-strength reading (ADX) is only 23, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G17" s="19" t="inlineStr">
@@ -70566,7 +70979,8 @@
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>* the stop is 10.2% away, so the position has to shrink to keep the dollar risk at $5k</t>
+          <t>* the stop is 10.2% away, so the position has to shrink to keep the dollar risk at $5k
+* trend-strength reading (ADX) is only 22, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G18" s="19" t="inlineStr">
@@ -70606,7 +71020,8 @@
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>* the stop is 9.6% away, so the position has to shrink to keep the dollar risk at $5k</t>
+          <t>* the stop is 9.6% away, so the position has to shrink to keep the dollar risk at $5k
+* trend-strength reading (ADX) is only 20, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G19" s="19" t="inlineStr">
@@ -70766,7 +71181,8 @@
       </c>
       <c r="F23" s="19" t="inlineStr">
         <is>
-          <t>* still repairing - price is +1.9% vs its 200-day average, so starter size only</t>
+          <t>* trend-strength reading (ADX) is only 21, under 27 - there is no trend here to ride
+* still repairing - price is +1.9% vs its 200-day average, so starter size only</t>
         </is>
       </c>
       <c r="G23" s="19" t="inlineStr">
@@ -70805,7 +71221,8 @@
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
-          <t>* still repairing - price is +15.1% vs its 200-day average, so starter size only</t>
+          <t>* trend-strength reading (ADX) is only 25, under 27 - there is no trend here to ride
+* still repairing - price is +15.1% vs its 200-day average, so starter size only</t>
         </is>
       </c>
       <c r="G24" s="19" t="inlineStr">
@@ -70845,7 +71262,8 @@
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>* still repairing - price is +12.1% vs its 200-day average, so starter size only</t>
+          <t>* trend-strength reading (ADX) is only 22, under 27 - there is no trend here to ride
+* still repairing - price is +12.1% vs its 200-day average, so starter size only</t>
         </is>
       </c>
       <c r="G25" s="19" t="inlineStr">
@@ -70885,7 +71303,8 @@
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
-          <t>* still repairing - price is +11.2% vs its 200-day average, so starter size only</t>
+          <t>* trend-strength reading (ADX) is only 22, under 27 - there is no trend here to ride
+* still repairing - price is +11.2% vs its 200-day average, so starter size only</t>
         </is>
       </c>
       <c r="G26" s="19" t="inlineStr">
@@ -70923,7 +71342,8 @@
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>* still repairing - price is +13.5% vs its 200-day average, so starter size only
+          <t>* trend-strength reading (ADX) is only 20, under 27 - there is no trend here to ride
+* still repairing - price is +13.5% vs its 200-day average, so starter size only
 * the signal fired TODAY - it can still un-print before the close, so treat it as provisional</t>
         </is>
       </c>
@@ -71168,7 +71588,8 @@
       <c r="F33" s="26" t="inlineStr">
         <is>
           <t>* the stop is only 1.5% below the price - an ordinary quiet day could knock the trade out
-* the stop sits 0.98 normal daily swings below the price (under 1.0) - routine wiggle will hit it with nothing actually going wrong</t>
+* the stop sits 0.98 normal daily swings below the price (under 1.0) - routine wiggle will hit it with nothing actually going wrong
+* trend-strength reading (ADX) is only 25, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G33" s="26" t="inlineStr">
@@ -71208,7 +71629,8 @@
       </c>
       <c r="F34" s="26" t="inlineStr">
         <is>
-          <t>* the stop sits 0.85 normal daily swings below the price (under 1.0) - routine wiggle will hit it with nothing actually going wrong</t>
+          <t>* the stop sits 0.85 normal daily swings below the price (under 1.0) - routine wiggle will hit it with nothing actually going wrong
+* trend-strength reading (ADX) is only 23, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G34" s="26" t="inlineStr">
@@ -71248,7 +71670,8 @@
       </c>
       <c r="F35" s="26" t="inlineStr">
         <is>
-          <t>* the stop is 12.4% away - keeping risk at $5k shrinks the position to a token</t>
+          <t>* the stop is 12.4% away - keeping risk at $5k shrinks the position to a token
+* trend-strength reading (ADX) is only 24, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G35" s="26" t="inlineStr">
@@ -71288,7 +71711,8 @@
       </c>
       <c r="F36" s="26" t="inlineStr">
         <is>
-          <t>* the stop is 14.1% away - keeping risk at $5k shrinks the position to a token</t>
+          <t>* the stop is 14.1% away - keeping risk at $5k shrinks the position to a token
+* trend-strength reading (ADX) is only 23, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G36" s="26" t="inlineStr">
@@ -71329,7 +71753,7 @@
       <c r="F37" s="26" t="inlineStr">
         <is>
           <t>* the stop is 22.0% away - keeping risk at $5k shrinks the position to a token
-* trend-strength reading (ADX) is only 19, under 20 - there is no trend here to ride</t>
+* trend-strength reading (ADX) is only 19, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G37" s="26" t="inlineStr">
@@ -71369,6 +71793,7 @@
       <c r="F38" s="26" t="inlineStr">
         <is>
           <t>* the stop is 12.3% away - keeping risk at $5k shrinks the position to a token
+* trend-strength reading (ADX) is only 23, under 27 - there is no trend here to ride
 * the signal fired TODAY - it can still un-print before the close, so treat it as provisional</t>
         </is>
       </c>
@@ -71410,7 +71835,7 @@
       <c r="F39" s="26" t="inlineStr">
         <is>
           <t>* the stop is 10.1% away, so the position has to shrink to keep the dollar risk at $5k
-* trend-strength reading (ADX) is only 19, under 20 - there is no trend here to ride</t>
+* trend-strength reading (ADX) is only 19, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G39" s="26" t="inlineStr">
@@ -71490,6 +71915,7 @@
       <c r="F41" s="26" t="inlineStr">
         <is>
           <t>* the stop is 36.3% away - keeping risk at $5k shrinks the position to a token
+* trend-strength reading (ADX) is only 24, under 27 - there is no trend here to ride
 * price is 26% above its trend line (ZLSMA) - stretched, a worse entry</t>
         </is>
       </c>
@@ -71530,7 +71956,8 @@
       </c>
       <c r="F42" s="26" t="inlineStr">
         <is>
-          <t>* the stop is 13.5% away - keeping risk at $5k shrinks the position to a token</t>
+          <t>* the stop is 13.5% away - keeping risk at $5k shrinks the position to a token
+* trend-strength reading (ADX) is only 21, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G42" s="26" t="inlineStr">
@@ -71651,7 +72078,7 @@
       <c r="F45" s="26" t="inlineStr">
         <is>
           <t>* the stop is 14.9% away - keeping risk at $5k shrinks the position to a token
-* trend-strength reading (ADX) is only 20, under 20 - there is no trend here to ride
+* trend-strength reading (ADX) is only 20, under 27 - there is no trend here to ride
 * price is 12% above its trend line (ZLSMA) - stretched, a worse entry
 * the signal fired TODAY - it can still un-print before the close, so treat it as provisional</t>
         </is>
@@ -71694,7 +72121,7 @@
       </c>
       <c r="F46" s="26" t="inlineStr">
         <is>
-          <t>* trend-strength reading (ADX) is only 18, under 20 - there is no trend here to ride</t>
+          <t>* trend-strength reading (ADX) is only 18, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G46" s="26" t="inlineStr">
@@ -71775,6 +72202,7 @@
       <c r="F48" s="26" t="inlineStr">
         <is>
           <t>* the stop is 12.5% away - keeping risk at $5k shrinks the position to a token
+* trend-strength reading (ADX) is only 22, under 27 - there is no trend here to ride
 * price is 16% above its trend line (ZLSMA) - stretched, a worse entry</t>
         </is>
       </c>
@@ -71815,7 +72243,7 @@
       </c>
       <c r="F49" s="26" t="inlineStr">
         <is>
-          <t>* trend-strength reading (ADX) is only 18, under 20 - there is no trend here to ride</t>
+          <t>* trend-strength reading (ADX) is only 18, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G49" s="26" t="inlineStr">
@@ -71896,7 +72324,8 @@
       </c>
       <c r="F51" s="26" t="inlineStr">
         <is>
-          <t>* the stop sits 0.83 normal daily swings below the price (under 1.0) - routine wiggle will hit it with nothing actually going wrong</t>
+          <t>* the stop sits 0.83 normal daily swings below the price (under 1.0) - routine wiggle will hit it with nothing actually going wrong
+* trend-strength reading (ADX) is only 20, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G51" s="26" t="inlineStr">
@@ -71975,7 +72404,8 @@
       </c>
       <c r="F53" s="26" t="inlineStr">
         <is>
-          <t>* sellers are in control - selling pressure 16 vs buying pressure 15</t>
+          <t>* trend-strength reading (ADX) is only 24, under 27 - there is no trend here to ride
+* sellers are in control - selling pressure 16 vs buying pressure 15</t>
         </is>
       </c>
       <c r="G53" s="26" t="inlineStr">
@@ -72014,7 +72444,7 @@
       </c>
       <c r="F54" s="26" t="inlineStr">
         <is>
-          <t>* trend-strength reading (ADX) is only 20, under 20 - there is no trend here to ride</t>
+          <t>* trend-strength reading (ADX) is only 20, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G54" s="26" t="inlineStr">
@@ -72054,7 +72484,7 @@
       <c r="F55" s="26" t="inlineStr">
         <is>
           <t>* the stop is only 2.0% below the price - an ordinary quiet day could knock the trade out
-* trend-strength reading (ADX) is only 20, under 20 - there is no trend here to ride</t>
+* trend-strength reading (ADX) is only 20, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G55" s="26" t="inlineStr">
@@ -72136,7 +72566,7 @@
       <c r="F57" s="26" t="inlineStr">
         <is>
           <t>* the stop sits 1.00 normal daily swings below the price (under 1.0) - routine wiggle will hit it with nothing actually going wrong
-* trend-strength reading (ADX) is only 17, under 20 - there is no trend here to ride</t>
+* trend-strength reading (ADX) is only 17, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G57" s="26" t="inlineStr">
@@ -72217,7 +72647,7 @@
       </c>
       <c r="F59" s="26" t="inlineStr">
         <is>
-          <t>* trend-strength reading (ADX) is only 20, under 20 - there is no trend here to ride
+          <t>* trend-strength reading (ADX) is only 20, under 27 - there is no trend here to ride
 * still repairing - price is +0.1% vs its 200-day average, so starter size only</t>
         </is>
       </c>
@@ -72258,7 +72688,7 @@
       <c r="F60" s="26" t="inlineStr">
         <is>
           <t>* the stop is only 0.8% below the price - an ordinary quiet day could knock the trade out
-* trend-strength reading (ADX) is only 15, under 20 - there is no trend here to ride</t>
+* trend-strength reading (ADX) is only 15, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G60" s="26" t="inlineStr">
@@ -72297,7 +72727,7 @@
       </c>
       <c r="F61" s="26" t="inlineStr">
         <is>
-          <t>* trend-strength reading (ADX) is only 16, under 20 - there is no trend here to ride</t>
+          <t>* trend-strength reading (ADX) is only 16, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G61" s="26" t="inlineStr">
@@ -72418,7 +72848,7 @@
       <c r="F64" s="26" t="inlineStr">
         <is>
           <t>* the stop is 24.1% away - keeping risk at $5k shrinks the position to a token
-* trend-strength reading (ADX) is only 16, under 20 - there is no trend here to ride
+* trend-strength reading (ADX) is only 16, under 27 - there is no trend here to ride
 * fails the long-term health check badly (-17.6% vs its 200-day average) - watch only, no size</t>
         </is>
       </c>
@@ -72460,7 +72890,7 @@
       <c r="F65" s="26" t="inlineStr">
         <is>
           <t>* the stop sits 0.76 normal daily swings below the price (under 1.0) - routine wiggle will hit it with nothing actually going wrong
-* trend-strength reading (ADX) is only 16, under 20 - there is no trend here to ride</t>
+* trend-strength reading (ADX) is only 16, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G65" s="26" t="inlineStr">
@@ -72498,6 +72928,7 @@
       <c r="F66" s="26" t="inlineStr">
         <is>
           <t>* the stop is 11.3% away, so the position has to shrink to keep the dollar risk at $5k
+* trend-strength reading (ADX) is only 20, under 27 - there is no trend here to ride
 * sellers are in control - selling pressure 17 vs buying pressure 16
 * price is 16% above its trend line (ZLSMA) - stretched, a worse entry</t>
         </is>
@@ -72537,7 +72968,7 @@
       </c>
       <c r="F67" s="26" t="inlineStr">
         <is>
-          <t>* trend-strength reading (ADX) is only 10, under 20 - there is no trend here to ride</t>
+          <t>* trend-strength reading (ADX) is only 10, under 27 - there is no trend here to ride</t>
         </is>
       </c>
       <c r="G67" s="26" t="inlineStr">
@@ -72697,7 +73128,7 @@
       <c r="F71" s="26" t="inlineStr">
         <is>
           <t>* the stop is 14.9% away - keeping risk at $5k shrinks the position to a token
-* trend-strength reading (ADX) is only 18, under 20 - there is no trend here to ride
+* trend-strength reading (ADX) is only 18, under 27 - there is no trend here to ride
 * still repairing - price is +15.4% vs its 200-day average, so starter size only
 * price is 19% above its trend line (ZLSMA) - stretched, a worse entry</t>
         </is>
@@ -72737,6 +73168,7 @@
       <c r="F72" s="26" t="inlineStr">
         <is>
           <t>* the stop sits 0.99 normal daily swings below the price (under 1.0) - routine wiggle will hit it with nothing actually going wrong
+* trend-strength reading (ADX) is only 25, under 27 - there is no trend here to ride
 * sellers are in control - selling pressure 20 vs buying pressure 17
 * still repairing - price is +19.0% vs its 200-day average, so starter size only</t>
         </is>
@@ -72777,6 +73209,7 @@
       <c r="F73" s="26" t="inlineStr">
         <is>
           <t>* the stop sits 0.82 normal daily swings below the price (under 1.0) - routine wiggle will hit it with nothing actually going wrong
+* trend-strength reading (ADX) is only 23, under 27 - there is no trend here to ride
 * sellers are in control - selling pressure 22 vs buying pressure 20
 * still repairing - price is +14.3% vs its 200-day average, so starter size only</t>
         </is>
@@ -72817,7 +73250,8 @@
       </c>
       <c r="F74" s="26" t="inlineStr">
         <is>
-          <t>* sellers are in control - selling pressure 17 vs buying pressure 16
+          <t>* trend-strength reading (ADX) is only 23, under 27 - there is no trend here to ride
+* sellers are in control - selling pressure 17 vs buying pressure 16
 * still repairing - price is +11.4% vs its 200-day average, so starter size only</t>
         </is>
       </c>
@@ -72858,7 +73292,7 @@
       <c r="F75" s="26" t="inlineStr">
         <is>
           <t>* the stop is 10.4% away, so the position has to shrink to keep the dollar risk at $5k
-* trend-strength reading (ADX) is only 12, under 20 - there is no trend here to ride
+* trend-strength reading (ADX) is only 12, under 27 - there is no trend here to ride
 * still repairing - price is -2.2% vs its 200-day average, so starter size only</t>
         </is>
       </c>
@@ -72899,7 +73333,7 @@
       <c r="F76" s="26" t="inlineStr">
         <is>
           <t>* the stop is 17.5% away - keeping risk at $5k shrinks the position to a token
-* trend-strength reading (ADX) is only 17, under 20 - there is no trend here to ride
+* trend-strength reading (ADX) is only 17, under 27 - there is no trend here to ride
 * price is 21% above its trend line (ZLSMA) - stretched, a worse entry</t>
         </is>
       </c>
@@ -72938,6 +73372,7 @@
       <c r="F77" s="26" t="inlineStr">
         <is>
           <t>* the stop is 12.2% away - keeping risk at $5k shrinks the position to a token
+* trend-strength reading (ADX) is only 24, under 27 - there is no trend here to ride
 * still repairing - price is -4.9% vs its 200-day average, so starter size only
 * price is 19% above its trend line (ZLSMA) - stretched, a worse entry</t>
         </is>
@@ -72978,7 +73413,7 @@
       </c>
       <c r="F78" s="26" t="inlineStr">
         <is>
-          <t>* trend-strength reading (ADX) is only 20, under 20 - there is no trend here to ride
+          <t>* trend-strength reading (ADX) is only 20, under 27 - there is no trend here to ride
 * still repairing - price is +23.2% vs its 200-day average, so starter size only</t>
         </is>
       </c>
@@ -73098,6 +73533,7 @@
       <c r="F81" s="26" t="inlineStr">
         <is>
           <t>* the stop is 14.6% away - keeping risk at $5k shrinks the position to a token
+* trend-strength reading (ADX) is only 22, under 27 - there is no trend here to ride
 * fails the long-term health check badly (-37.6% vs its 200-day average) - watch only, no size
 * price is 16% above its trend line (ZLSMA) - stretched, a worse entry</t>
         </is>
@@ -73138,7 +73574,7 @@
       </c>
       <c r="F82" s="26" t="inlineStr">
         <is>
-          <t>* trend-strength reading (ADX) is only 16, under 20 - there is no trend here to ride
+          <t>* trend-strength reading (ADX) is only 16, under 27 - there is no trend here to ride
 * still repairing - price is +15.5% vs its 200-day average, so starter size only</t>
         </is>
       </c>
@@ -73220,7 +73656,7 @@
       <c r="F84" s="26" t="inlineStr">
         <is>
           <t>* the stop sits 0.97 normal daily swings below the price (under 1.0) - routine wiggle will hit it with nothing actually going wrong
-* trend-strength reading (ADX) is only 18, under 20 - there is no trend here to ride
+* trend-strength reading (ADX) is only 18, under 27 - there is no trend here to ride
 * fails the long-term health check badly (-13.1% vs its 200-day average) - watch only, no size</t>
         </is>
       </c>
@@ -73260,7 +73696,7 @@
       <c r="F85" s="26" t="inlineStr">
         <is>
           <t>* the stop is 13.6% away - keeping risk at $5k shrinks the position to a token
-* trend-strength reading (ADX) is only 15, under 20 - there is no trend here to ride
+* trend-strength reading (ADX) is only 15, under 27 - there is no trend here to ride
 * still repairing - price is -6.2% vs its 200-day average, so starter size only
 * the signal fired TODAY - it can still un-print before the close, so treat it as provisional</t>
         </is>
@@ -73380,6 +73816,7 @@
       <c r="F88" s="26" t="inlineStr">
         <is>
           <t>* the stop is 17.0% away - keeping risk at $5k shrinks the position to a token
+* trend-strength reading (ADX) is only 25, under 27 - there is no trend here to ride
 * still repairing - price is +29.5% vs its 200-day average, so starter size only
 * price is 29% above its trend line (ZLSMA) - stretched, a worse entry</t>
         </is>
@@ -73418,7 +73855,7 @@
       </c>
       <c r="F89" s="26" t="inlineStr">
         <is>
-          <t>* trend-strength reading (ADX) is only 19, under 20 - there is no trend here to ride
+          <t>* trend-strength reading (ADX) is only 19, under 27 - there is no trend here to ride
 * sellers are in control - selling pressure 19 vs buying pressure 19
 * fails the long-term health check badly (-10.7% vs its 200-day average) - watch only, no size
 * the signal fired TODAY - it can still un-print before the close, so treat it as provisional</t>
@@ -73459,6 +73896,7 @@
       <c r="F90" s="26" t="inlineStr">
         <is>
           <t>* the stop is 10.3% away, so the position has to shrink to keep the dollar risk at $5k
+* trend-strength reading (ADX) is only 24, under 27 - there is no trend here to ride
 * sellers are in control - selling pressure 18 vs buying pressure 15
 * fails the long-term health check badly (-31.7% vs its 200-day average) - watch only, no size
 * price is 22% above its trend line (ZLSMA) - stretched, a worse entry</t>
@@ -73501,6 +73939,7 @@
       <c r="F91" s="26" t="inlineStr">
         <is>
           <t>* the stop is 9.1% away, so the position has to shrink to keep the dollar risk at $5k
+* trend-strength reading (ADX) is only 24, under 27 - there is no trend here to ride
 * price is 0.8% BELOW its trend line (ZLSMA) - the turn up has not actually happened yet</t>
         </is>
       </c>
@@ -73659,7 +74098,8 @@
       </c>
       <c r="F95" s="26" t="inlineStr">
         <is>
-          <t>* price is 3.0% BELOW its trend line (ZLSMA) - the turn up has not actually happened yet</t>
+          <t>* trend-strength reading (ADX) is only 23, under 27 - there is no trend here to ride
+* price is 3.0% BELOW its trend line (ZLSMA) - the turn up has not actually happened yet</t>
         </is>
       </c>
       <c r="G95" s="26" t="inlineStr">
@@ -73738,7 +74178,8 @@
       </c>
       <c r="F97" s="26" t="inlineStr">
         <is>
-          <t>* price is 2.6% BELOW its trend line (ZLSMA) - the turn up has not actually happened yet</t>
+          <t>* trend-strength reading (ADX) is only 23, under 27 - there is no trend here to ride
+* price is 2.6% BELOW its trend line (ZLSMA) - the turn up has not actually happened yet</t>
         </is>
       </c>
       <c r="G97" s="26" t="inlineStr">
@@ -73857,6 +74298,7 @@
       <c r="F100" s="26" t="inlineStr">
         <is>
           <t>* the stop is 11.3% away, so the position has to shrink to keep the dollar risk at $5k
+* trend-strength reading (ADX) is only 23, under 27 - there is no trend here to ride
 * price is 0.7% BELOW its trend line (ZLSMA) - the turn up has not actually happened yet</t>
         </is>
       </c>
@@ -74018,6 +74460,7 @@
         <is>
           <t>* the stop is only 0.4% below the price - an ordinary quiet day could knock the trade out
 * the stop sits 0.15 normal daily swings below the price (under 1.0) - routine wiggle will hit it with nothing actually going wrong
+* trend-strength reading (ADX) is only 24, under 27 - there is no trend here to ride
 * price is 0.1% BELOW its trend line (ZLSMA) - the turn up has not actually happened yet</t>
         </is>
       </c>
@@ -74058,7 +74501,7 @@
       <c r="F105" s="26" t="inlineStr">
         <is>
           <t>* the stop sits 1.00 normal daily swings below the price (under 1.0) - routine wiggle will hit it with nothing actually going wrong
-* trend-strength reading (ADX) is only 20, under 20 - there is no trend here to ride
+* trend-strength reading (ADX) is only 20, under 27 - there is no trend here to ride
 * price is 1.8% BELOW its trend line (ZLSMA) - the turn up has not actually happened yet</t>
         </is>
       </c>
@@ -74096,7 +74539,8 @@
       </c>
       <c r="F106" s="26" t="inlineStr">
         <is>
-          <t>* still repairing - price is +8.2% vs its 200-day average, so starter size only
+          <t>* trend-strength reading (ADX) is only 24, under 27 - there is no trend here to ride
+* still repairing - price is +8.2% vs its 200-day average, so starter size only
 * price is 2.6% BELOW its trend line (ZLSMA) - the turn up has not actually happened yet</t>
         </is>
       </c>
@@ -74135,7 +74579,7 @@
       <c r="F107" s="26" t="inlineStr">
         <is>
           <t>* the stop sits 0.96 normal daily swings below the price (under 1.0) - routine wiggle will hit it with nothing actually going wrong
-* trend-strength reading (ADX) is only 19, under 20 - there is no trend here to ride
+* trend-strength reading (ADX) is only 19, under 27 - there is no trend here to ride
 * price is 0.4% BELOW its trend line (ZLSMA) - the turn up has not actually happened yet</t>
         </is>
       </c>
@@ -74216,7 +74660,7 @@
       </c>
       <c r="F109" s="26" t="inlineStr">
         <is>
-          <t>* trend-strength reading (ADX) is only 17, under 20 - there is no trend here to ride
+          <t>* trend-strength reading (ADX) is only 17, under 27 - there is no trend here to ride
 * still repairing - price is -0.2% vs its 200-day average, so starter size only
 * price is 0.0% BELOW its trend line (ZLSMA) - the turn up has not actually happened yet</t>
         </is>
@@ -74256,6 +74700,7 @@
       <c r="F110" s="26" t="inlineStr">
         <is>
           <t>* the stop is 12.1% away - keeping risk at $5k shrinks the position to a token
+* trend-strength reading (ADX) is only 21, under 27 - there is no trend here to ride
 * fails the long-term health check badly (-46.8% vs its 200-day average) - watch only, no size
 * price is 14.5% BELOW its trend line (ZLSMA) - the turn up has not actually happened yet
 * too thinly traded - about $724,048 changes hands daily, not enough to get a $85,000 order in and out cleanly</t>
@@ -74295,6 +74740,7 @@
       <c r="F111" s="26" t="inlineStr">
         <is>
           <t>* the stop sits 0.94 normal daily swings below the price (under 1.0) - routine wiggle will hit it with nothing actually going wrong
+* trend-strength reading (ADX) is only 21, under 27 - there is no trend here to ride
 * sellers are in control - selling pressure 23 vs buying pressure 17
 * fails the long-term health check badly (-12.5% vs its 200-day average) - watch only, no size
 * price is 3.6% BELOW its trend line (ZLSMA) - the turn up has not actually happened yet</t>
@@ -74334,7 +74780,7 @@
       <c r="F112" s="26" t="inlineStr">
         <is>
           <t>* the stop sits 0.89 normal daily swings below the price (under 1.0) - routine wiggle will hit it with nothing actually going wrong
-* trend-strength reading (ADX) is only 15, under 20 - there is no trend here to ride
+* trend-strength reading (ADX) is only 15, under 27 - there is no trend here to ride
 * sellers are in control - selling pressure 20 vs buying pressure 20
 * still repairing - price is +9.0% vs its 200-day average, so starter size only
 * price is 3.4% BELOW its trend line (ZLSMA) - the turn up has not actually happened yet</t>
